--- a/22_Quantitative_Systematic/instances/benchmark_reference_costed.xlsx
+++ b/22_Quantitative_Systematic/instances/benchmark_reference_costed.xlsx
@@ -9,17 +9,25 @@
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Backtest" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Performance" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Walk Forward" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Costs &amp; Capacity" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Risk" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Stress" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Checks" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Sources" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="RefreshLog" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Institutional Surface" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Challenge Log" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Lineage Map" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Backtest" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Performance" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Walk Forward" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Costs &amp; Capacity" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Risk" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Stress" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Checks" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Sources" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="RefreshLog" sheetId="14" state="visible" r:id="rId16"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" name="FS_DOMAIN" vbProcedure="false">'Institutional Surface'!$C$5</definedName>
+    <definedName function="false" hidden="false" name="FS_MATURITY" vbProcedure="false">'Institutional Surface'!$C$6</definedName>
+    <definedName function="false" hidden="false" name="FS_MODEL_ID" vbProcedure="false">'Institutional Surface'!$C$4</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -30,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="279">
   <si>
     <t xml:space="preserve">[STRATEGY] — Systematic Research Model</t>
   </si>
@@ -104,6 +112,303 @@
     <t xml:space="preserve">PASS / REVIEW / FAIL must remain visible</t>
   </si>
   <si>
+    <t xml:space="preserve">Quantitative &amp; Systematic — Institutional Decision Surface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantitative &amp; Systematic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Declared maturity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canonical builder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tools/builders/build_quant_release.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision arena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research, portfolio construction, execution, risk and model validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Committee artifact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research approval and live-monitoring pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating cadence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per research run; daily live; monthly model committee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key decision outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence / location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gross and net performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">capacity and market impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">walk-forward stability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base, downside and break-even outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liquidity / funding requirement and binding constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insider questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What data was knowable at decision time?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which result survives alternate costs and universes?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where is capacity constrained—signal or execution?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which assumption is owner-approved versus modeler judgement?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What fails first and who must act?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario families</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cost and impact inflation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regime break</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crowding and correlation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data freshness / source failure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">combined severe-but-plausible downside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary diligence documents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research specification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data dictionary and licenses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">experiment and code version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">approved model card and assumption register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">independent validation and challenge record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenge tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no look-ahead or survivorship bias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">walk-forward partitions do not overlap improperly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gross return exceeds net by explicit costs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source-to-model lineage is reproducible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">units, signs, dates and legal definitions reconcile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Known failure modes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">optimizing on one backtest path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">using revised fundamentals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ignoring rejected orders and partial fills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stale vintage presented as current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decision output disconnected from a binding constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulatory / methodological anchors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applicability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Reserve SR 26-2 Model Risk Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">governance, validation, change control, monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.federalreserve.gov/supervisionreg/srletters/SR2602.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map explicitly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basel MAR21 Sensitivities-Based Method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market-risk factors and aggregation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bis.org/basel_framework/chapter/MAR/21.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Challenge, Override and Closure Log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source, Transformation, Ownership and Refresh Map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System / provider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As-of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downstream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per dataset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">point-in-time and survivorship controls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TO MAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">daily/intraday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">versioned feature lineage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model governance evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">version, reviewer, sign-off and change log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decision-use snapshot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immutable as-of date and source receipt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Backtest, Cost, and Capacity Assumptions</t>
   </si>
   <si>
@@ -443,9 +748,6 @@
     <t xml:space="preserve">Check</t>
   </si>
   <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
     <t xml:space="preserve">Signal lag is positive</t>
   </si>
   <si>
@@ -482,9 +784,6 @@
     <t xml:space="preserve">Source URL or document</t>
   </si>
   <si>
-    <t xml:space="preserve">As-of</t>
-  </si>
-  <si>
     <t xml:space="preserve">Notes / transformation</t>
   </si>
   <si>
@@ -549,9 +848,6 @@
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
   </si>
   <si>
     <t xml:space="preserve">Trigger</t>
@@ -597,7 +893,7 @@
     <numFmt numFmtId="172" formatCode="0.0\x;[RED]\(0.0&quot;x)&quot;;\-"/>
     <numFmt numFmtId="173" formatCode="0.000\x"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -675,6 +971,29 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="15"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="Arial"/>
@@ -682,7 +1001,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -692,7 +1011,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
+        <bgColor rgb="FF17365D"/>
       </patternFill>
     </fill>
     <fill>
@@ -707,8 +1026,20 @@
         <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+        <bgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -722,6 +1053,15 @@
       <top/>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
       </bottom>
       <diagonal/>
     </border>
@@ -751,7 +1091,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -792,6 +1132,30 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -800,7 +1164,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -808,7 +1172,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -820,7 +1184,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -832,7 +1196,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -844,7 +1208,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -852,7 +1216,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -953,11 +1317,11 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFD9EAF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFB7B7B7"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -982,7 +1346,7 @@
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF17365D"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF111827"/>
       <rgbColor rgb="FF333300"/>
@@ -1316,6 +1680,511 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:E13"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" s="33" t="n">
+        <f aca="false">-PERCENTILE(Backtest!H5:H64,1-Assumptions!E15)</f>
+        <v>0.0144585090902402</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C6" s="33" t="n">
+        <f aca="false">IFERROR(-AVERAGEIF(Backtest!H5:H64,"&lt;="&amp;-C5,Backtest!H5:H64),0)</f>
+        <v>0.018812308289703</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <f aca="false">-(AVERAGE(Backtest!H5:H64)+NORMSINV(1-Assumptions!E15)*STDEVP(Backtest!H5:H64))</f>
+        <v>0.0168512012830348</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <f aca="false">Performance!D9</f>
+        <v>-0.151661943459633</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <f aca="false">ABS(Assumptions!E17)</f>
+        <v>0.2</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f aca="false">IF(C8&lt;=C9,"PASS","BREACH")</f>
+        <v>PASS</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C11" s="33" t="n">
+        <f aca="false">Performance!D6</f>
+        <v>0.0365679857703514</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C12" s="33" t="n">
+        <f aca="false">Assumptions!E16</f>
+        <v>0.12</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C13" s="35" t="n">
+        <f aca="false">IFERROR(C12/C11,0)</f>
+        <v>3.2815589229772</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:E2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>C10="PASS"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>C10="FAIL"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>C10="REVIEW"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>C10="BREACH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:G9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D5" s="39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E5" s="39" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F5" s="33" t="n">
+        <f aca="false">AVERAGE(Backtest!D5:D64)*D5*Assumptions!$E$7/10000+Assumptions!$E$8*(AVERAGE(Backtest!D5:D64)*D5*Assumptions!$E$9/(Assumptions!$E$10*E5))^1.5</f>
+        <v>0.000624497631362428</v>
+      </c>
+      <c r="G5" s="33" t="n">
+        <f aca="false">C5-F5</f>
+        <v>-0.120624497631362</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="D6" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="33" t="n">
+        <f aca="false">AVERAGE(Backtest!D5:D64)*D6*Assumptions!$E$7/10000+Assumptions!$E$8*(AVERAGE(Backtest!D5:D64)*D6*Assumptions!$E$9/(Assumptions!$E$10*E6))^1.5</f>
+        <v>0.000902745455956885</v>
+      </c>
+      <c r="G6" s="33" t="n">
+        <f aca="false">C6-F6</f>
+        <v>-0.0609027454559569</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D7" s="39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <f aca="false">AVERAGE(Backtest!D5:D64)*D7*Assumptions!$E$7/10000+Assumptions!$E$8*(AVERAGE(Backtest!D5:D64)*D7*Assumptions!$E$9/(Assumptions!$E$10*E7))^1.5</f>
+        <v>0.00185794073027529</v>
+      </c>
+      <c r="G7" s="33" t="n">
+        <f aca="false">C7-F7</f>
+        <v>-0.101857940730275</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="D8" s="39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E8" s="39" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F8" s="33" t="n">
+        <f aca="false">AVERAGE(Backtest!D5:D64)*D8*Assumptions!$E$7/10000+Assumptions!$E$8*(AVERAGE(Backtest!D5:D64)*D8*Assumptions!$E$9/(Assumptions!$E$10*E8))^1.5</f>
+        <v>0.00133493401017127</v>
+      </c>
+      <c r="G8" s="33" t="n">
+        <f aca="false">C8-F8</f>
+        <v>-0.0413349340101713</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="D9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <f aca="false">AVERAGE(Backtest!D5:D64)*D9*Assumptions!$E$7/10000+Assumptions!$E$8*(AVERAGE(Backtest!D5:D64)*D9*Assumptions!$E$9/(Assumptions!$E$10*E9))^1.5</f>
+        <v>0.000374346542046622</v>
+      </c>
+      <c r="G9" s="33" t="n">
+        <f aca="false">C9-F9</f>
+        <v>-0.0303743465420466</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:G2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:C13"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <f aca="false">IF(Assumptions!E18&gt;=1,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <f aca="false">IF(Assumptions!E19=1,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f aca="false">IF(AND(Assumptions!E7&gt;0,Assumptions!E8&gt;0),"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f aca="false">IF('Costs &amp; Capacity'!C14="PASS","PASS","BREACH")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <f aca="false">IF(Performance!C5&gt;=Performance!D5,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f aca="false">IF(COUNT('Walk Forward'!H5:H10)=6,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <f aca="false">IF(Risk!C10="PASS","PASS","REVIEW")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="1" t="str">
+        <f aca="false">IF(COUNT(Backtest!H5:H64)=60,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C13" s="1" t="str">
+        <f aca="false">IF(COUNTIF(C5:C12,"FAIL")=0,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:C2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:C13">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>C5="PASS"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>C5="FAIL"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>C5="REVIEW"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>C5="BREACH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:E10"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1328,108 +2197,108 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>147</v>
+        <v>245</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>151</v>
+      <c r="B4" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="34" t="s">
-        <v>152</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>153</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>155</v>
+      <c r="B5" s="40" t="s">
+        <v>249</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>158</v>
+      <c r="B6" s="40" t="s">
+        <v>253</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="34" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>162</v>
+      <c r="B7" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="34" t="s">
-        <v>163</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>164</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>165</v>
+      <c r="B8" s="40" t="s">
+        <v>260</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>261</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>167</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>168</v>
+      <c r="B9" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>258</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>170</v>
-      </c>
-      <c r="D10" s="35" t="s">
+      <c r="B10" s="41" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>267</v>
+      </c>
+      <c r="D10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="35" t="s">
-        <v>171</v>
+      <c r="E10" s="41" t="s">
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -1446,7 +2315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1465,7 +2334,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>172</v>
+        <v>269</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1474,236 +2343,236 @@
       <c r="G2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>178</v>
+      <c r="B4" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="36" t="s">
-        <v>179</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>170</v>
-      </c>
-      <c r="E5" s="36" t="s">
-        <v>180</v>
-      </c>
-      <c r="F5" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="G5" s="36" t="s">
-        <v>182</v>
+      <c r="C5" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="E5" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="G5" s="42" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
+      <c r="B9" s="42"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
+      <c r="B10" s="42"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
+      <c r="B11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="36"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="36"/>
-      <c r="C24" s="36"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="36"/>
-      <c r="C26" s="36"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="36"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="36"/>
-      <c r="G29" s="36"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1724,6 +2593,1070 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:F63"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E61" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F61" s="14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F63" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B60:F60"/>
+  </mergeCells>
+  <dataValidations count="6">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F14:F18" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F22:F26" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F30:F34" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F38:F42" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F46:F50" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F54:F58" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:I9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H54" type="list">
+      <formula1>"OPEN,IN REVIEW,REMEDIATED,ACCEPTED RISK,CLOSED"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G54" type="list">
+      <formula1>"LOW,MEDIUM,HIGH,CRITICAL"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:J8"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="15" t="s">
+        <v>113</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:J2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J5:J40" type="list">
+      <formula1>"TO MAP,ACTIVE,STALE,EXCEPTION,RETIRED"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1735,7 +3668,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1743,290 +3676,290 @@
       <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="B4" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>28</v>
+      <c r="D4" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="C5" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="18" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D5,C5)</f>
         <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="13" t="n">
+        <v>130</v>
+      </c>
+      <c r="C6" s="19" t="n">
         <v>0.002</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="19" t="n">
         <v>0.002</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="20" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D6,C6)</f>
         <v>0.002</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="15" t="n">
+        <v>132</v>
+      </c>
+      <c r="C7" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="23" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D7,C7)</f>
         <v>10</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="18" t="n">
+        <v>134</v>
+      </c>
+      <c r="C8" s="24" t="n">
         <v>0.003</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="25" t="n">
         <v>0.008</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D8,C8)</f>
         <v>0.003</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="21" t="n">
+        <v>136</v>
+      </c>
+      <c r="C9" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="28" t="n">
         <v>150</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="29" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D9,C9)</f>
         <v>60</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>38</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="22" t="n">
+        <v>138</v>
+      </c>
+      <c r="C10" s="28" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="28" t="n">
         <v>250</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="29" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D10,C10)</f>
         <v>500</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>38</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="24" t="n">
+        <v>139</v>
+      </c>
+      <c r="C11" s="30" t="n">
         <v>0.1</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="30" t="n">
         <v>0.08</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="31" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D11,C11)</f>
         <v>0.1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="11" t="n">
+        <v>141</v>
+      </c>
+      <c r="C12" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="18" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D12,C12)</f>
         <v>24</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="11" t="n">
+        <v>142</v>
+      </c>
+      <c r="C13" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="18" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D13,C13)</f>
         <v>6</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>30</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="11" t="n">
+        <v>143</v>
+      </c>
+      <c r="C14" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="18" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D14,C14)</f>
         <v>6</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>30</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="24" t="n">
+        <v>144</v>
+      </c>
+      <c r="C15" s="30" t="n">
         <v>0.95</v>
       </c>
-      <c r="D15" s="24" t="n">
+      <c r="D15" s="30" t="n">
         <v>0.99</v>
       </c>
-      <c r="E15" s="25" t="n">
+      <c r="E15" s="31" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D15,C15)</f>
         <v>0.95</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="24" t="n">
+        <v>145</v>
+      </c>
+      <c r="C16" s="30" t="n">
         <v>0.12</v>
       </c>
-      <c r="D16" s="24" t="n">
+      <c r="D16" s="30" t="n">
         <v>0.1</v>
       </c>
-      <c r="E16" s="25" t="n">
+      <c r="E16" s="31" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D16,C16)</f>
         <v>0.12</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="24" t="n">
+        <v>147</v>
+      </c>
+      <c r="C17" s="30" t="n">
         <v>-0.2</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="30" t="n">
         <v>-0.15</v>
       </c>
-      <c r="E17" s="25" t="n">
+      <c r="E17" s="31" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D17,C17)</f>
         <v>-0.2</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>32</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="12" t="n">
+        <v>148</v>
+      </c>
+      <c r="C18" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="18" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D18,C18)</f>
         <v>1</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>30</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="12" t="n">
+        <v>149</v>
+      </c>
+      <c r="C19" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="18" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D19,C19)</f>
         <v>1</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>51</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2043,7 +3976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2062,7 +3995,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>52</v>
+        <v>151</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2076,79 +4009,79 @@
       <c r="L2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>63</v>
+      <c r="B4" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="19" t="n">
         <v>0.0118652159242335</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="19" t="n">
         <v>0.279800399619259</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="33" t="n">
         <f aca="false">ABS(D5)*Assumptions!$E$7/10000</f>
         <v>0.000279800399619259</v>
       </c>
-      <c r="G5" s="27" t="n">
+      <c r="G5" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D5)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>1.84571915522619E-005</v>
       </c>
-      <c r="H5" s="27" t="n">
+      <c r="H5" s="33" t="n">
         <f aca="false">IF(E5=1,C5-F5-G5,0)</f>
         <v>0.011566958333062</v>
       </c>
-      <c r="I5" s="28" t="n">
+      <c r="I5" s="34" t="n">
         <f aca="false">1+H5</f>
         <v>1.01156695833306</v>
       </c>
-      <c r="J5" s="28" t="n">
+      <c r="J5" s="34" t="n">
         <f aca="false">I5</f>
         <v>1.01156695833306</v>
       </c>
-      <c r="K5" s="27" t="n">
+      <c r="K5" s="33" t="n">
         <f aca="false">IFERROR(I5/J5-1,0)</f>
         <v>0</v>
       </c>
-      <c r="L5" s="27" t="n">
+      <c r="L5" s="33" t="n">
         <f aca="false">ABS(D5)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0335760479543111</v>
       </c>
@@ -2157,41 +4090,41 @@
       <c r="B6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="19" t="n">
         <v>0.0151772011235084</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="19" t="n">
         <v>0.308412751346298</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="33" t="n">
         <f aca="false">ABS(D6)*Assumptions!$E$7/10000</f>
         <v>0.000308412751346298</v>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D6)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.13595260739215E-005</v>
       </c>
-      <c r="H6" s="27" t="n">
+      <c r="H6" s="33" t="n">
         <f aca="false">IF(E6=1,C6-F6-G6,0)</f>
         <v>0.0148474288460882</v>
       </c>
-      <c r="I6" s="28" t="n">
+      <c r="I6" s="34" t="n">
         <f aca="false">I5*(1+H6)</f>
         <v>1.02658612676997</v>
       </c>
-      <c r="J6" s="28" t="n">
+      <c r="J6" s="34" t="n">
         <f aca="false">MAX(J5,I6)</f>
         <v>1.02658612676997</v>
       </c>
-      <c r="K6" s="27" t="n">
+      <c r="K6" s="33" t="n">
         <f aca="false">IFERROR(I6/J6-1,0)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="27" t="n">
+      <c r="L6" s="33" t="n">
         <f aca="false">ABS(D6)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0370095301615558</v>
       </c>
@@ -2200,41 +4133,41 @@
       <c r="B7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="19" t="n">
         <v>0.0175550139277398</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="19" t="n">
         <v>0.334696371009255</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="33" t="n">
         <f aca="false">ABS(D7)*Assumptions!$E$7/10000</f>
         <v>0.000334696371009255</v>
       </c>
-      <c r="G7" s="27" t="n">
+      <c r="G7" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D7)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.41473584542045E-005</v>
       </c>
-      <c r="H7" s="27" t="n">
+      <c r="H7" s="33" t="n">
         <f aca="false">IF(E7=1,C7-F7-G7,0)</f>
         <v>0.0171961701982763</v>
       </c>
-      <c r="I7" s="28" t="n">
+      <c r="I7" s="34" t="n">
         <f aca="false">I6*(1+H7)</f>
         <v>1.04423947652909</v>
       </c>
-      <c r="J7" s="28" t="n">
+      <c r="J7" s="34" t="n">
         <f aca="false">MAX(J6,I7)</f>
         <v>1.04423947652909</v>
       </c>
-      <c r="K7" s="27" t="n">
+      <c r="K7" s="33" t="n">
         <f aca="false">IFERROR(I7/J7-1,0)</f>
         <v>0</v>
       </c>
-      <c r="L7" s="27" t="n">
+      <c r="L7" s="33" t="n">
         <f aca="false">ABS(D7)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0401635645211106</v>
       </c>
@@ -2243,41 +4176,41 @@
       <c r="B8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="19" t="n">
         <v>0.0187100300968512</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="19" t="n">
         <v>0.357603413634928</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="33" t="n">
         <f aca="false">ABS(D8)*Assumptions!$E$7/10000</f>
         <v>0.000357603413634928</v>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D8)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.66683169228015E-005</v>
       </c>
-      <c r="H8" s="27" t="n">
+      <c r="H8" s="33" t="n">
         <f aca="false">IF(E8=1,C8-F8-G8,0)</f>
         <v>0.0183257583662935</v>
       </c>
-      <c r="I8" s="28" t="n">
+      <c r="I8" s="34" t="n">
         <f aca="false">I7*(1+H8)</f>
         <v>1.06337595685251</v>
       </c>
-      <c r="J8" s="28" t="n">
+      <c r="J8" s="34" t="n">
         <f aca="false">MAX(J7,I8)</f>
         <v>1.06337595685251</v>
       </c>
-      <c r="K8" s="27" t="n">
+      <c r="K8" s="33" t="n">
         <f aca="false">IFERROR(I8/J8-1,0)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="27" t="n">
+      <c r="L8" s="33" t="n">
         <f aca="false">ABS(D8)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0429124096361914</v>
       </c>
@@ -2286,41 +4219,41 @@
       <c r="B9" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="19" t="n">
         <v>0.00847826357322536</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="19" t="n">
         <v>0.376220647721185</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="33" t="n">
         <f aca="false">ABS(D9)*Assumptions!$E$7/10000</f>
         <v>0.000376220647721185</v>
       </c>
-      <c r="G9" s="27" t="n">
+      <c r="G9" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D9)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.87777651440983E-005</v>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="33" t="n">
         <f aca="false">IF(E9=1,C9-F9-G9,0)</f>
         <v>0.00807326516036008</v>
       </c>
-      <c r="I9" s="28" t="n">
+      <c r="I9" s="34" t="n">
         <f aca="false">I8*(1+H9)</f>
         <v>1.07196087291733</v>
       </c>
-      <c r="J9" s="28" t="n">
+      <c r="J9" s="34" t="n">
         <f aca="false">MAX(J8,I9)</f>
         <v>1.07196087291733</v>
       </c>
-      <c r="K9" s="27" t="n">
+      <c r="K9" s="33" t="n">
         <f aca="false">IFERROR(I9/J9-1,0)</f>
         <v>0</v>
       </c>
-      <c r="L9" s="27" t="n">
+      <c r="L9" s="33" t="n">
         <f aca="false">ABS(D9)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0451464777265422</v>
       </c>
@@ -2329,41 +4262,41 @@
       <c r="B10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="19" t="n">
         <v>0.0168391695219598</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="19" t="n">
         <v>0.389805862895084</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F10" s="27" t="n">
+      <c r="F10" s="33" t="n">
         <f aca="false">ABS(D10)*Assumptions!$E$7/10000</f>
         <v>0.000389805862895084</v>
       </c>
-      <c r="G10" s="27" t="n">
+      <c r="G10" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D10)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.03504876974076E-005</v>
       </c>
-      <c r="H10" s="27" t="n">
+      <c r="H10" s="33" t="n">
         <f aca="false">IF(E10=1,C10-F10-G10,0)</f>
         <v>0.0164190131713673</v>
       </c>
-      <c r="I10" s="28" t="n">
+      <c r="I10" s="34" t="n">
         <f aca="false">I9*(1+H10)</f>
         <v>1.08956141260895</v>
       </c>
-      <c r="J10" s="28" t="n">
+      <c r="J10" s="34" t="n">
         <f aca="false">MAX(J9,I10)</f>
         <v>1.08956141260895</v>
       </c>
-      <c r="K10" s="27" t="n">
+      <c r="K10" s="33" t="n">
         <f aca="false">IFERROR(I10/J10-1,0)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="27" t="n">
+      <c r="L10" s="33" t="n">
         <f aca="false">ABS(D10)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0467767035474101</v>
       </c>
@@ -2372,41 +4305,41 @@
       <c r="B11" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="19" t="n">
         <v>0.0139188444160687</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="19" t="n">
         <v>0.397817459498269</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F11" s="27" t="n">
+      <c r="F11" s="33" t="n">
         <f aca="false">ABS(D11)*Assumptions!$E$7/10000</f>
         <v>0.000397817459498269</v>
       </c>
-      <c r="G11" s="27" t="n">
+      <c r="G11" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D11)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.12909596975841E-005</v>
       </c>
-      <c r="H11" s="27" t="n">
+      <c r="H11" s="33" t="n">
         <f aca="false">IF(E11=1,C11-F11-G11,0)</f>
         <v>0.0134897359968728</v>
       </c>
-      <c r="I11" s="28" t="n">
+      <c r="I11" s="34" t="n">
         <f aca="false">I10*(1+H11)</f>
         <v>1.10425930841743</v>
       </c>
-      <c r="J11" s="28" t="n">
+      <c r="J11" s="34" t="n">
         <f aca="false">MAX(J10,I11)</f>
         <v>1.10425930841743</v>
       </c>
-      <c r="K11" s="27" t="n">
+      <c r="K11" s="33" t="n">
         <f aca="false">IFERROR(I11/J11-1,0)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="27" t="n">
+      <c r="L11" s="33" t="n">
         <f aca="false">ABS(D11)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0477380951397923</v>
       </c>
@@ -2415,41 +4348,41 @@
       <c r="B12" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="19" t="n">
         <v>0.00997725176355615</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="19" t="n">
         <v>0.399936040456226</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F12" s="27" t="n">
+      <c r="F12" s="33" t="n">
         <f aca="false">ABS(D12)*Assumptions!$E$7/10000</f>
         <v>0.000399936040456226</v>
       </c>
-      <c r="G12" s="27" t="n">
+      <c r="G12" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D12)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.15412526844547E-005</v>
       </c>
-      <c r="H12" s="27" t="n">
+      <c r="H12" s="33" t="n">
         <f aca="false">IF(E12=1,C12-F12-G12,0)</f>
         <v>0.00954577447041547</v>
       </c>
-      <c r="I12" s="28" t="n">
+      <c r="I12" s="34" t="n">
         <f aca="false">I11*(1+H12)</f>
         <v>1.11480031873244</v>
       </c>
-      <c r="J12" s="28" t="n">
+      <c r="J12" s="34" t="n">
         <f aca="false">MAX(J11,I12)</f>
         <v>1.11480031873244</v>
       </c>
-      <c r="K12" s="27" t="n">
+      <c r="K12" s="33" t="n">
         <f aca="false">IFERROR(I12/J12-1,0)</f>
         <v>0</v>
       </c>
-      <c r="L12" s="27" t="n">
+      <c r="L12" s="33" t="n">
         <f aca="false">ABS(D12)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0479923248547471</v>
       </c>
@@ -2458,41 +4391,41 @@
       <c r="B13" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="19" t="n">
         <v>0.00538085718888648</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="19" t="n">
         <v>0.396077144631729</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F13" s="27" t="n">
+      <c r="F13" s="33" t="n">
         <f aca="false">ABS(D13)*Assumptions!$E$7/10000</f>
         <v>0.000396077144631729</v>
       </c>
-      <c r="G13" s="27" t="n">
+      <c r="G13" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D13)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.1085853608681E-005</v>
       </c>
-      <c r="H13" s="27" t="n">
+      <c r="H13" s="33" t="n">
         <f aca="false">IF(E13=1,C13-F13-G13,0)</f>
         <v>0.00495369419064607</v>
       </c>
-      <c r="I13" s="28" t="n">
+      <c r="I13" s="34" t="n">
         <f aca="false">I12*(1+H13)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="J13" s="28" t="n">
+      <c r="J13" s="34" t="n">
         <f aca="false">MAX(J12,I13)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K13" s="27" t="n">
+      <c r="K13" s="33" t="n">
         <f aca="false">IFERROR(I13/J13-1,0)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="27" t="n">
+      <c r="L13" s="33" t="n">
         <f aca="false">ABS(D13)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0475292573558075</v>
       </c>
@@ -2501,41 +4434,41 @@
       <c r="B14" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="19" t="n">
         <v>-0.00943634017096778</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="19" t="n">
         <v>0.386394614023852</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F14" s="27" t="n">
+      <c r="F14" s="33" t="n">
         <f aca="false">ABS(D14)*Assumptions!$E$7/10000</f>
         <v>0.000386394614023852</v>
       </c>
-      <c r="G14" s="27" t="n">
+      <c r="G14" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D14)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.99529581693538E-005</v>
       </c>
-      <c r="H14" s="27" t="n">
+      <c r="H14" s="33" t="n">
         <f aca="false">IF(E14=1,C14-F14-G14,0)</f>
         <v>-0.00985268774316099</v>
       </c>
-      <c r="I14" s="28" t="n">
+      <c r="I14" s="34" t="n">
         <f aca="false">I13*(1+H14)</f>
         <v>1.10928450887424</v>
       </c>
-      <c r="J14" s="28" t="n">
+      <c r="J14" s="34" t="n">
         <f aca="false">MAX(J13,I14)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K14" s="27" t="n">
+      <c r="K14" s="33" t="n">
         <f aca="false">IFERROR(I14/J14-1,0)</f>
         <v>-0.00985268774316095</v>
       </c>
-      <c r="L14" s="27" t="n">
+      <c r="L14" s="33" t="n">
         <f aca="false">ABS(D14)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0463673536828622</v>
       </c>
@@ -2544,41 +4477,41 @@
       <c r="B15" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="19" t="n">
         <v>-0.00401911805060946</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="19" t="n">
         <v>0.371274460572939</v>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F15" s="27" t="n">
+      <c r="F15" s="33" t="n">
         <f aca="false">ABS(D15)*Assumptions!$E$7/10000</f>
         <v>0.000371274460572939</v>
       </c>
-      <c r="G15" s="27" t="n">
+      <c r="G15" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D15)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.82121209746804E-005</v>
       </c>
-      <c r="H15" s="27" t="n">
+      <c r="H15" s="33" t="n">
         <f aca="false">IF(E15=1,C15-F15-G15,0)</f>
         <v>-0.00441860463215708</v>
       </c>
-      <c r="I15" s="28" t="n">
+      <c r="I15" s="34" t="n">
         <f aca="false">I14*(1+H15)</f>
         <v>1.10438301920495</v>
       </c>
-      <c r="J15" s="28" t="n">
+      <c r="J15" s="34" t="n">
         <f aca="false">MAX(J14,I15)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K15" s="27" t="n">
+      <c r="K15" s="33" t="n">
         <f aca="false">IFERROR(I15/J15-1,0)</f>
         <v>-0.014227757243617</v>
       </c>
-      <c r="L15" s="27" t="n">
+      <c r="L15" s="33" t="n">
         <f aca="false">ABS(D15)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0445529352687527</v>
       </c>
@@ -2587,41 +4520,41 @@
       <c r="B16" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="19" t="n">
         <v>-0.00793961497619996</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="19" t="n">
         <v>0.351319477082673</v>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F16" s="27" t="n">
+      <c r="F16" s="33" t="n">
         <f aca="false">ABS(D16)*Assumptions!$E$7/10000</f>
         <v>0.000351319477082673</v>
       </c>
-      <c r="G16" s="27" t="n">
+      <c r="G16" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D16)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.59684761282271E-005</v>
       </c>
-      <c r="H16" s="27" t="n">
+      <c r="H16" s="33" t="n">
         <f aca="false">IF(E16=1,C16-F16-G16,0)</f>
         <v>-0.00831690292941086</v>
       </c>
-      <c r="I16" s="28" t="n">
+      <c r="I16" s="34" t="n">
         <f aca="false">I15*(1+H16)</f>
         <v>1.09519797283733</v>
       </c>
-      <c r="J16" s="28" t="n">
+      <c r="J16" s="34" t="n">
         <f aca="false">MAX(J15,I16)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K16" s="27" t="n">
+      <c r="K16" s="33" t="n">
         <f aca="false">IFERROR(I16/J16-1,0)</f>
         <v>-0.0224263292971295</v>
       </c>
-      <c r="L16" s="27" t="n">
+      <c r="L16" s="33" t="n">
         <f aca="false">ABS(D16)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0421583372499208</v>
       </c>
@@ -2630,41 +4563,41 @@
       <c r="B17" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="19" t="n">
         <v>-0.0108428704725758</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="19" t="n">
         <v>0.32732520577322</v>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F17" s="27" t="n">
+      <c r="F17" s="33" t="n">
         <f aca="false">ABS(D17)*Assumptions!$E$7/10000</f>
         <v>0.00032732520577322</v>
       </c>
-      <c r="G17" s="27" t="n">
+      <c r="G17" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D17)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.33540549723553E-005</v>
       </c>
-      <c r="H17" s="27" t="n">
+      <c r="H17" s="33" t="n">
         <f aca="false">IF(E17=1,C17-F17-G17,0)</f>
         <v>-0.0111935497333214</v>
       </c>
-      <c r="I17" s="28" t="n">
+      <c r="I17" s="34" t="n">
         <f aca="false">I16*(1+H17)</f>
         <v>1.08293881986054</v>
       </c>
-      <c r="J17" s="28" t="n">
+      <c r="J17" s="34" t="n">
         <f aca="false">MAX(J16,I17)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K17" s="27" t="n">
+      <c r="K17" s="33" t="n">
         <f aca="false">IFERROR(I17/J17-1,0)</f>
         <v>-0.0333688487981277</v>
       </c>
-      <c r="L17" s="27" t="n">
+      <c r="L17" s="33" t="n">
         <f aca="false">ABS(D17)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0392790246927864</v>
       </c>
@@ -2673,41 +4606,41 @@
       <c r="B18" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="19" t="n">
         <v>-0.012484340024458</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="19" t="n">
         <v>0.300248222523386</v>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F18" s="27" t="n">
+      <c r="F18" s="33" t="n">
         <f aca="false">ABS(D18)*Assumptions!$E$7/10000</f>
         <v>0.000300248222523386</v>
       </c>
-      <c r="G18" s="27" t="n">
+      <c r="G18" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D18)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.05169968306081E-005</v>
       </c>
-      <c r="H18" s="27" t="n">
+      <c r="H18" s="33" t="n">
         <f aca="false">IF(E18=1,C18-F18-G18,0)</f>
         <v>-0.012805105243812</v>
       </c>
-      <c r="I18" s="28" t="n">
+      <c r="I18" s="34" t="n">
         <f aca="false">I17*(1+H18)</f>
         <v>1.06907167429962</v>
       </c>
-      <c r="J18" s="28" t="n">
+      <c r="J18" s="34" t="n">
         <f aca="false">MAX(J17,I18)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K18" s="27" t="n">
+      <c r="K18" s="33" t="n">
         <f aca="false">IFERROR(I18/J18-1,0)</f>
         <v>-0.0457466624212148</v>
       </c>
-      <c r="L18" s="27" t="n">
+      <c r="L18" s="33" t="n">
         <f aca="false">ABS(D18)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0360297867028063</v>
       </c>
@@ -2716,41 +4649,41 @@
       <c r="B19" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="19" t="n">
         <v>-0.0227552867239183</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="19" t="n">
         <v>0.27116800120898</v>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F19" s="27" t="n">
+      <c r="F19" s="33" t="n">
         <f aca="false">ABS(D19)*Assumptions!$E$7/10000</f>
         <v>0.00027116800120898</v>
       </c>
-      <c r="G19" s="27" t="n">
+      <c r="G19" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D19)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>1.76096524095471E-005</v>
       </c>
-      <c r="H19" s="27" t="n">
+      <c r="H19" s="33" t="n">
         <f aca="false">IF(E19=1,C19-F19-G19,0)</f>
         <v>-0.0230440643775368</v>
       </c>
-      <c r="I19" s="28" t="n">
+      <c r="I19" s="34" t="n">
         <f aca="false">I18*(1+H19)</f>
         <v>1.04443591781286</v>
       </c>
-      <c r="J19" s="28" t="n">
+      <c r="J19" s="34" t="n">
         <f aca="false">MAX(J18,I19)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K19" s="27" t="n">
+      <c r="K19" s="33" t="n">
         <f aca="false">IFERROR(I19/J19-1,0)</f>
         <v>-0.0677365377648598</v>
       </c>
-      <c r="L19" s="27" t="n">
+      <c r="L19" s="33" t="n">
         <f aca="false">ABS(D19)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0325401601450776</v>
       </c>
@@ -2759,41 +4692,41 @@
       <c r="B20" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="19" t="n">
         <v>-0.011693285493763</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="19" t="n">
         <v>0.258756121514137</v>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F20" s="27" t="n">
+      <c r="F20" s="33" t="n">
         <f aca="false">ABS(D20)*Assumptions!$E$7/10000</f>
         <v>0.000258756121514137</v>
       </c>
-      <c r="G20" s="27" t="n">
+      <c r="G20" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D20)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>1.64145534755818E-005</v>
       </c>
-      <c r="H20" s="27" t="n">
+      <c r="H20" s="33" t="n">
         <f aca="false">IF(E20=1,C20-F20-G20,0)</f>
         <v>-0.0119684561687527</v>
       </c>
-      <c r="I20" s="28" t="n">
+      <c r="I20" s="34" t="n">
         <f aca="false">I19*(1+H20)</f>
         <v>1.03193563230944</v>
       </c>
-      <c r="J20" s="28" t="n">
+      <c r="J20" s="34" t="n">
         <f aca="false">MAX(J19,I20)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K20" s="27" t="n">
+      <c r="K20" s="33" t="n">
         <f aca="false">IFERROR(I20/J20-1,0)</f>
         <v>-0.0788942921503507</v>
       </c>
-      <c r="L20" s="27" t="n">
+      <c r="L20" s="33" t="n">
         <f aca="false">ABS(D20)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0310507345816964</v>
       </c>
@@ -2802,41 +4735,41 @@
       <c r="B21" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="19" t="n">
         <v>-0.00947671338935732</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="19" t="n">
         <v>0.288331165304025</v>
       </c>
-      <c r="E21" s="27" t="n">
+      <c r="E21" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F21" s="27" t="n">
+      <c r="F21" s="33" t="n">
         <f aca="false">ABS(D21)*Assumptions!$E$7/10000</f>
         <v>0.000288331165304025</v>
       </c>
-      <c r="G21" s="27" t="n">
+      <c r="G21" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D21)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>1.93076983277298E-005</v>
       </c>
-      <c r="H21" s="27" t="n">
+      <c r="H21" s="33" t="n">
         <f aca="false">IF(E21=1,C21-F21-G21,0)</f>
         <v>-0.00978435225298908</v>
       </c>
-      <c r="I21" s="28" t="n">
+      <c r="I21" s="34" t="n">
         <f aca="false">I20*(1+H21)</f>
         <v>1.02183881058051</v>
       </c>
-      <c r="J21" s="28" t="n">
+      <c r="J21" s="34" t="n">
         <f aca="false">MAX(J20,I21)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K21" s="27" t="n">
+      <c r="K21" s="33" t="n">
         <f aca="false">IFERROR(I21/J21-1,0)</f>
         <v>-0.0879067148581905</v>
       </c>
-      <c r="L21" s="27" t="n">
+      <c r="L21" s="33" t="n">
         <f aca="false">ABS(D21)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.034599739836483</v>
       </c>
@@ -2845,41 +4778,41 @@
       <c r="B22" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C22" s="13" t="n">
+      <c r="C22" s="19" t="n">
         <v>-0.0064038604974068</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="19" t="n">
         <v>0.316378066494228</v>
       </c>
-      <c r="E22" s="27" t="n">
+      <c r="E22" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F22" s="27" t="n">
+      <c r="F22" s="33" t="n">
         <f aca="false">ABS(D22)*Assumptions!$E$7/10000</f>
         <v>0.000316378066494228</v>
       </c>
-      <c r="G22" s="27" t="n">
+      <c r="G22" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D22)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.21923184224645E-005</v>
       </c>
-      <c r="H22" s="27" t="n">
+      <c r="H22" s="33" t="n">
         <f aca="false">IF(E22=1,C22-F22-G22,0)</f>
         <v>-0.00674243088232349</v>
       </c>
-      <c r="I22" s="28" t="n">
+      <c r="I22" s="34" t="n">
         <f aca="false">I21*(1+H22)</f>
         <v>1.0149491330273</v>
       </c>
-      <c r="J22" s="28" t="n">
+      <c r="J22" s="34" t="n">
         <f aca="false">MAX(J21,I22)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K22" s="27" t="n">
+      <c r="K22" s="33" t="n">
         <f aca="false">IFERROR(I22/J22-1,0)</f>
         <v>-0.0940564407914906</v>
       </c>
-      <c r="L22" s="27" t="n">
+      <c r="L22" s="33" t="n">
         <f aca="false">ABS(D22)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0379653679793074</v>
       </c>
@@ -2888,41 +4821,41 @@
       <c r="B23" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="19" t="n">
         <v>-0.00285898654454352</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="19" t="n">
         <v>0.341778683641408</v>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E23" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F23" s="27" t="n">
+      <c r="F23" s="33" t="n">
         <f aca="false">ABS(D23)*Assumptions!$E$7/10000</f>
         <v>0.000341778683641408</v>
       </c>
-      <c r="G23" s="27" t="n">
+      <c r="G23" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D23)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.49178509060429E-005</v>
       </c>
-      <c r="H23" s="27" t="n">
+      <c r="H23" s="33" t="n">
         <f aca="false">IF(E23=1,C23-F23-G23,0)</f>
         <v>-0.00322568307909097</v>
       </c>
-      <c r="I23" s="28" t="n">
+      <c r="I23" s="34" t="n">
         <f aca="false">I22*(1+H23)</f>
         <v>1.01167522878276</v>
       </c>
-      <c r="J23" s="28" t="n">
+      <c r="J23" s="34" t="n">
         <f aca="false">MAX(J22,I23)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K23" s="27" t="n">
+      <c r="K23" s="33" t="n">
         <f aca="false">IFERROR(I23/J23-1,0)</f>
         <v>-0.0969787276010409</v>
       </c>
-      <c r="L23" s="27" t="n">
+      <c r="L23" s="33" t="n">
         <f aca="false">ABS(D23)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.041013442036969</v>
       </c>
@@ -2931,41 +4864,41 @@
       <c r="B24" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="C24" s="13" t="n">
+      <c r="C24" s="19" t="n">
         <v>-0.0092690824404773</v>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="19" t="n">
         <v>0.363520374296189</v>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F24" s="27" t="n">
+      <c r="F24" s="33" t="n">
         <f aca="false">ABS(D24)*Assumptions!$E$7/10000</f>
         <v>0.000363520374296189</v>
       </c>
-      <c r="G24" s="27" t="n">
+      <c r="G24" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D24)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.73329344031032E-005</v>
       </c>
-      <c r="H24" s="27" t="n">
+      <c r="H24" s="33" t="n">
         <f aca="false">IF(E24=1,C24-F24-G24,0)</f>
         <v>-0.00965993574917659</v>
       </c>
-      <c r="I24" s="28" t="n">
+      <c r="I24" s="34" t="n">
         <f aca="false">I23*(1+H24)</f>
         <v>1.00190251107368</v>
       </c>
-      <c r="J24" s="28" t="n">
+      <c r="J24" s="34" t="n">
         <f aca="false">MAX(J23,I24)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K24" s="27" t="n">
+      <c r="K24" s="33" t="n">
         <f aca="false">IFERROR(I24/J24-1,0)</f>
         <v>-0.105701855072554</v>
       </c>
-      <c r="L24" s="27" t="n">
+      <c r="L24" s="33" t="n">
         <f aca="false">ABS(D24)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0436224449155427</v>
       </c>
@@ -2974,41 +4907,41 @@
       <c r="B25" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="19" t="n">
         <v>0.0039438842050228</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="19" t="n">
         <v>0.380736365862038</v>
       </c>
-      <c r="E25" s="27" t="n">
+      <c r="E25" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F25" s="27" t="n">
+      <c r="F25" s="33" t="n">
         <f aca="false">ABS(D25)*Assumptions!$E$7/10000</f>
         <v>0.000380736365862038</v>
       </c>
-      <c r="G25" s="27" t="n">
+      <c r="G25" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D25)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.92974393681319E-005</v>
       </c>
-      <c r="H25" s="27" t="n">
+      <c r="H25" s="33" t="n">
         <f aca="false">IF(E25=1,C25-F25-G25,0)</f>
         <v>0.00353385039979263</v>
       </c>
-      <c r="I25" s="28" t="n">
+      <c r="I25" s="34" t="n">
         <f aca="false">I24*(1+H25)</f>
         <v>1.00544308466299</v>
       </c>
-      <c r="J25" s="28" t="n">
+      <c r="J25" s="34" t="n">
         <f aca="false">MAX(J24,I25)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K25" s="27" t="n">
+      <c r="K25" s="33" t="n">
         <f aca="false">IFERROR(I25/J25-1,0)</f>
         <v>-0.102541539215569</v>
       </c>
-      <c r="L25" s="27" t="n">
+      <c r="L25" s="33" t="n">
         <f aca="false">ABS(D25)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0456883639034446</v>
       </c>
@@ -3017,41 +4950,41 @@
       <c r="B26" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C26" s="19" t="n">
         <v>0.00640996723222435</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="19" t="n">
         <v>0.392740311083427</v>
       </c>
-      <c r="E26" s="27" t="n">
+      <c r="E26" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F26" s="27" t="n">
+      <c r="F26" s="33" t="n">
         <f aca="false">ABS(D26)*Assumptions!$E$7/10000</f>
         <v>0.000392740311083427</v>
       </c>
-      <c r="G26" s="27" t="n">
+      <c r="G26" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D26)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.06938483791975E-005</v>
       </c>
-      <c r="H26" s="27" t="n">
+      <c r="H26" s="33" t="n">
         <f aca="false">IF(E26=1,C26-F26-G26,0)</f>
         <v>0.00598653307276173</v>
       </c>
-      <c r="I26" s="28" t="n">
+      <c r="I26" s="34" t="n">
         <f aca="false">I25*(1+H26)</f>
         <v>1.01146220294211</v>
       </c>
-      <c r="J26" s="28" t="n">
+      <c r="J26" s="34" t="n">
         <f aca="false">MAX(J25,I26)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K26" s="27" t="n">
+      <c r="K26" s="33" t="n">
         <f aca="false">IFERROR(I26/J26-1,0)</f>
         <v>-0.0971688744586531</v>
       </c>
-      <c r="L26" s="27" t="n">
+      <c r="L26" s="33" t="n">
         <f aca="false">ABS(D26)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0471288373300112</v>
       </c>
@@ -3060,41 +4993,41 @@
       <c r="B27" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="C27" s="13" t="n">
+      <c r="C27" s="19" t="n">
         <v>0.00785229879394966</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="19" t="n">
         <v>0.39905365054502</v>
       </c>
-      <c r="E27" s="27" t="n">
+      <c r="E27" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F27" s="27" t="n">
+      <c r="F27" s="33" t="n">
         <f aca="false">ABS(D27)*Assumptions!$E$7/10000</f>
         <v>0.00039905365054502</v>
       </c>
-      <c r="G27" s="27" t="n">
+      <c r="G27" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D27)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.14369247798415E-005</v>
       </c>
-      <c r="H27" s="27" t="n">
+      <c r="H27" s="33" t="n">
         <f aca="false">IF(E27=1,C27-F27-G27,0)</f>
         <v>0.0074218082186248</v>
       </c>
-      <c r="I27" s="28" t="n">
+      <c r="I27" s="34" t="n">
         <f aca="false">I26*(1+H27)</f>
         <v>1.01896908143273</v>
       </c>
-      <c r="J27" s="28" t="n">
+      <c r="J27" s="34" t="n">
         <f aca="false">MAX(J26,I27)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K27" s="27" t="n">
+      <c r="K27" s="33" t="n">
         <f aca="false">IFERROR(I27/J27-1,0)</f>
         <v>-0.09046823499108</v>
       </c>
-      <c r="L27" s="27" t="n">
+      <c r="L27" s="33" t="n">
         <f aca="false">ABS(D27)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0478864380654024</v>
       </c>
@@ -3103,41 +5036,41 @@
       <c r="B28" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C28" s="13" t="n">
+      <c r="C28" s="19" t="n">
         <v>0.00811767839814802</v>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="19" t="n">
         <v>0.399424691325376</v>
       </c>
-      <c r="E28" s="27" t="n">
+      <c r="E28" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F28" s="27" t="n">
+      <c r="F28" s="33" t="n">
         <f aca="false">ABS(D28)*Assumptions!$E$7/10000</f>
         <v>0.000399424691325376</v>
       </c>
-      <c r="G28" s="27" t="n">
+      <c r="G28" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D28)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.14807801313343E-005</v>
       </c>
-      <c r="H28" s="27" t="n">
+      <c r="H28" s="33" t="n">
         <f aca="false">IF(E28=1,C28-F28-G28,0)</f>
         <v>0.00768677292669131</v>
       </c>
-      <c r="I28" s="28" t="n">
+      <c r="I28" s="34" t="n">
         <f aca="false">I27*(1+H28)</f>
         <v>1.02680166538102</v>
       </c>
-      <c r="J28" s="28" t="n">
+      <c r="J28" s="34" t="n">
         <f aca="false">MAX(J27,I28)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K28" s="27" t="n">
+      <c r="K28" s="33" t="n">
         <f aca="false">IFERROR(I28/J28-1,0)</f>
         <v>-0.0834768708438437</v>
       </c>
-      <c r="L28" s="27" t="n">
+      <c r="L28" s="33" t="n">
         <f aca="false">ABS(D28)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0479309629590451</v>
       </c>
@@ -3146,41 +5079,41 @@
       <c r="B29" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="19" t="n">
         <v>-0.00280667553386828</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="19" t="n">
         <v>0.393838641199471</v>
       </c>
-      <c r="E29" s="27" t="n">
+      <c r="E29" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F29" s="27" t="n">
+      <c r="F29" s="33" t="n">
         <f aca="false">ABS(D29)*Assumptions!$E$7/10000</f>
         <v>0.000393838641199471</v>
       </c>
-      <c r="G29" s="27" t="n">
+      <c r="G29" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D29)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.0822695109578E-005</v>
       </c>
-      <c r="H29" s="27" t="n">
+      <c r="H29" s="33" t="n">
         <f aca="false">IF(E29=1,C29-F29-G29,0)</f>
         <v>-0.00323133687017733</v>
       </c>
-      <c r="I29" s="28" t="n">
+      <c r="I29" s="34" t="n">
         <f aca="false">I28*(1+H29)</f>
         <v>1.02348372330132</v>
       </c>
-      <c r="J29" s="28" t="n">
+      <c r="J29" s="34" t="n">
         <f aca="false">MAX(J28,I29)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K29" s="27" t="n">
+      <c r="K29" s="33" t="n">
         <f aca="false">IFERROR(I29/J29-1,0)</f>
         <v>-0.0864384658234562</v>
       </c>
-      <c r="L29" s="27" t="n">
+      <c r="L29" s="33" t="n">
         <f aca="false">ABS(D29)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0472606369439365</v>
       </c>
@@ -3189,41 +5122,41 @@
       <c r="B30" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="C30" s="13" t="n">
+      <c r="C30" s="19" t="n">
         <v>0.0052079466088486</v>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="19" t="n">
         <v>0.382518198358023</v>
       </c>
-      <c r="E30" s="27" t="n">
+      <c r="E30" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F30" s="27" t="n">
+      <c r="F30" s="33" t="n">
         <f aca="false">ABS(D30)*Assumptions!$E$7/10000</f>
         <v>0.000382518198358023</v>
       </c>
-      <c r="G30" s="27" t="n">
+      <c r="G30" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D30)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.95033462521482E-005</v>
       </c>
-      <c r="H30" s="27" t="n">
+      <c r="H30" s="33" t="n">
         <f aca="false">IF(E30=1,C30-F30-G30,0)</f>
         <v>0.00479592506423843</v>
       </c>
-      <c r="I30" s="28" t="n">
+      <c r="I30" s="34" t="n">
         <f aca="false">I29*(1+H30)</f>
         <v>1.02839227454274</v>
       </c>
-      <c r="J30" s="28" t="n">
+      <c r="J30" s="34" t="n">
         <f aca="false">MAX(J29,I30)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K30" s="27" t="n">
+      <c r="K30" s="33" t="n">
         <f aca="false">IFERROR(I30/J30-1,0)</f>
         <v>-0.0820570931639748</v>
       </c>
-      <c r="L30" s="27" t="n">
+      <c r="L30" s="33" t="n">
         <f aca="false">ABS(D30)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0459021838029628</v>
       </c>
@@ -3232,41 +5165,41 @@
       <c r="B31" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C31" s="13" t="n">
+      <c r="C31" s="19" t="n">
         <v>0.00241702739946968</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="19" t="n">
         <v>0.365914673133398</v>
       </c>
-      <c r="E31" s="27" t="n">
+      <c r="E31" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F31" s="27" t="n">
+      <c r="F31" s="33" t="n">
         <f aca="false">ABS(D31)*Assumptions!$E$7/10000</f>
         <v>0.000365914673133398</v>
       </c>
-      <c r="G31" s="27" t="n">
+      <c r="G31" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D31)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.76034179531026E-005</v>
       </c>
-      <c r="H31" s="27" t="n">
+      <c r="H31" s="33" t="n">
         <f aca="false">IF(E31=1,C31-F31-G31,0)</f>
         <v>0.00202350930838318</v>
       </c>
-      <c r="I31" s="28" t="n">
+      <c r="I31" s="34" t="n">
         <f aca="false">I30*(1+H31)</f>
         <v>1.03047323588295</v>
       </c>
-      <c r="J31" s="28" t="n">
+      <c r="J31" s="34" t="n">
         <f aca="false">MAX(J30,I31)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K31" s="27" t="n">
+      <c r="K31" s="33" t="n">
         <f aca="false">IFERROR(I31/J31-1,0)</f>
         <v>-0.0801996271474278</v>
       </c>
-      <c r="L31" s="27" t="n">
+      <c r="L31" s="33" t="n">
         <f aca="false">ABS(D31)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0439097607760078</v>
       </c>
@@ -3275,41 +5208,41 @@
       <c r="B32" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="C32" s="13" t="n">
+      <c r="C32" s="19" t="n">
         <v>-0.000826054898524681</v>
       </c>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="19" t="n">
         <v>0.344689995680848</v>
       </c>
-      <c r="E32" s="27" t="n">
+      <c r="E32" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F32" s="27" t="n">
+      <c r="F32" s="33" t="n">
         <f aca="false">ABS(D32)*Assumptions!$E$7/10000</f>
         <v>0.000344689995680848</v>
       </c>
-      <c r="G32" s="27" t="n">
+      <c r="G32" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D32)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.52369078341005E-005</v>
       </c>
-      <c r="H32" s="27" t="n">
+      <c r="H32" s="33" t="n">
         <f aca="false">IF(E32=1,C32-F32-G32,0)</f>
         <v>-0.00119598180203963</v>
       </c>
-      <c r="I32" s="28" t="n">
+      <c r="I32" s="34" t="n">
         <f aca="false">I31*(1+H32)</f>
         <v>1.02924080864534</v>
       </c>
-      <c r="J32" s="28" t="n">
+      <c r="J32" s="34" t="n">
         <f aca="false">MAX(J31,I32)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K32" s="27" t="n">
+      <c r="K32" s="33" t="n">
         <f aca="false">IFERROR(I32/J32-1,0)</f>
         <v>-0.0812996916548687</v>
       </c>
-      <c r="L32" s="27" t="n">
+      <c r="L32" s="33" t="n">
         <f aca="false">ABS(D32)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0413627994817018</v>
       </c>
@@ -3318,41 +5251,41 @@
       <c r="B33" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="C33" s="13" t="n">
+      <c r="C33" s="19" t="n">
         <v>-0.0041098683365781</v>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="19" t="n">
         <v>0.319690326912064</v>
       </c>
-      <c r="E33" s="27" t="n">
+      <c r="E33" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F33" s="27" t="n">
+      <c r="F33" s="33" t="n">
         <f aca="false">ABS(D33)*Assumptions!$E$7/10000</f>
         <v>0.000319690326912064</v>
       </c>
-      <c r="G33" s="27" t="n">
+      <c r="G33" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D33)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.25417364251668E-005</v>
       </c>
-      <c r="H33" s="27" t="n">
+      <c r="H33" s="33" t="n">
         <f aca="false">IF(E33=1,C33-F33-G33,0)</f>
         <v>-0.00445210039991533</v>
       </c>
-      <c r="I33" s="28" t="n">
+      <c r="I33" s="34" t="n">
         <f aca="false">I32*(1+H33)</f>
         <v>1.02465852522956</v>
       </c>
-      <c r="J33" s="28" t="n">
+      <c r="J33" s="34" t="n">
         <f aca="false">MAX(J32,I33)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K33" s="27" t="n">
+      <c r="K33" s="33" t="n">
         <f aca="false">IFERROR(I33/J33-1,0)</f>
         <v>-0.0853898376650545</v>
       </c>
-      <c r="L33" s="27" t="n">
+      <c r="L33" s="33" t="n">
         <f aca="false">ABS(D33)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0383628392294477</v>
       </c>
@@ -3361,41 +5294,41 @@
       <c r="B34" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C34" s="13" t="n">
+      <c r="C34" s="19" t="n">
         <v>-0.0170113288179311</v>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="19" t="n">
         <v>0.291912324729839</v>
       </c>
-      <c r="E34" s="27" t="n">
+      <c r="E34" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F34" s="27" t="n">
+      <c r="F34" s="33" t="n">
         <f aca="false">ABS(D34)*Assumptions!$E$7/10000</f>
         <v>0.000291912324729839</v>
       </c>
-      <c r="G34" s="27" t="n">
+      <c r="G34" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D34)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>1.96685240497932E-005</v>
       </c>
-      <c r="H34" s="27" t="n">
+      <c r="H34" s="33" t="n">
         <f aca="false">IF(E34=1,C34-F34-G34,0)</f>
         <v>-0.0173229096667107</v>
       </c>
-      <c r="I34" s="28" t="n">
+      <c r="I34" s="34" t="n">
         <f aca="false">I33*(1+H34)</f>
         <v>1.00690845815778</v>
       </c>
-      <c r="J34" s="28" t="n">
+      <c r="J34" s="34" t="n">
         <f aca="false">MAX(J33,I34)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K34" s="27" t="n">
+      <c r="K34" s="33" t="n">
         <f aca="false">IFERROR(I34/J34-1,0)</f>
         <v>-0.101233546887438</v>
       </c>
-      <c r="L34" s="27" t="n">
+      <c r="L34" s="33" t="n">
         <f aca="false">ABS(D34)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0350294789675807</v>
       </c>
@@ -3404,41 +5337,41 @@
       <c r="B35" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="C35" s="13" t="n">
+      <c r="C35" s="19" t="n">
         <v>-0.00914353041562147</v>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="19" t="n">
         <v>0.262463410422624</v>
       </c>
-      <c r="E35" s="27" t="n">
+      <c r="E35" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F35" s="27" t="n">
+      <c r="F35" s="33" t="n">
         <f aca="false">ABS(D35)*Assumptions!$E$7/10000</f>
         <v>0.000262463410422624</v>
       </c>
-      <c r="G35" s="27" t="n">
+      <c r="G35" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D35)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>1.67685795441756E-005</v>
       </c>
-      <c r="H35" s="27" t="n">
+      <c r="H35" s="33" t="n">
         <f aca="false">IF(E35=1,C35-F35-G35,0)</f>
         <v>-0.00942276240558827</v>
       </c>
-      <c r="I35" s="28" t="n">
+      <c r="I35" s="34" t="n">
         <f aca="false">I34*(1+H35)</f>
         <v>0.997420598992387</v>
       </c>
-      <c r="J35" s="28" t="n">
+      <c r="J35" s="34" t="n">
         <f aca="false">MAX(J34,I35)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K35" s="27" t="n">
+      <c r="K35" s="33" t="n">
         <f aca="false">IFERROR(I35/J35-1,0)</f>
         <v>-0.109702409633231</v>
       </c>
-      <c r="L35" s="27" t="n">
+      <c r="L35" s="33" t="n">
         <f aca="false">ABS(D35)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0314956092507149</v>
       </c>
@@ -3447,41 +5380,41 @@
       <c r="B36" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="C36" s="13" t="n">
+      <c r="C36" s="19" t="n">
         <v>-0.0101997134567755</v>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D36" s="19" t="n">
         <v>0.267482380727574</v>
       </c>
-      <c r="E36" s="27" t="n">
+      <c r="E36" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F36" s="27" t="n">
+      <c r="F36" s="33" t="n">
         <f aca="false">ABS(D36)*Assumptions!$E$7/10000</f>
         <v>0.000267482380727574</v>
       </c>
-      <c r="G36" s="27" t="n">
+      <c r="G36" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D36)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>1.72518587529854E-005</v>
       </c>
-      <c r="H36" s="27" t="n">
+      <c r="H36" s="33" t="n">
         <f aca="false">IF(E36=1,C36-F36-G36,0)</f>
         <v>-0.0104844476962561</v>
       </c>
-      <c r="I36" s="28" t="n">
+      <c r="I36" s="34" t="n">
         <f aca="false">I35*(1+H36)</f>
         <v>0.986963194891083</v>
       </c>
-      <c r="J36" s="28" t="n">
+      <c r="J36" s="34" t="n">
         <f aca="false">MAX(J35,I36)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K36" s="27" t="n">
+      <c r="K36" s="33" t="n">
         <f aca="false">IFERROR(I36/J36-1,0)</f>
         <v>-0.119036688153534</v>
       </c>
-      <c r="L36" s="27" t="n">
+      <c r="L36" s="33" t="n">
         <f aca="false">ABS(D36)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0320978856873089</v>
       </c>
@@ -3490,41 +5423,41 @@
       <c r="B37" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="C37" s="13" t="n">
+      <c r="C37" s="19" t="n">
         <v>-0.00998850208202598</v>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="19" t="n">
         <v>0.296731204527007</v>
       </c>
-      <c r="E37" s="27" t="n">
+      <c r="E37" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F37" s="27" t="n">
+      <c r="F37" s="33" t="n">
         <f aca="false">ABS(D37)*Assumptions!$E$7/10000</f>
         <v>0.000296731204527007</v>
       </c>
-      <c r="G37" s="27" t="n">
+      <c r="G37" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D37)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.01575596244107E-005</v>
       </c>
-      <c r="H37" s="27" t="n">
+      <c r="H37" s="33" t="n">
         <f aca="false">IF(E37=1,C37-F37-G37,0)</f>
         <v>-0.0103053908461774</v>
       </c>
-      <c r="I37" s="28" t="n">
+      <c r="I37" s="34" t="n">
         <f aca="false">I36*(1+H37)</f>
         <v>0.976792153416938</v>
       </c>
-      <c r="J37" s="28" t="n">
+      <c r="J37" s="34" t="n">
         <f aca="false">MAX(J36,I37)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K37" s="27" t="n">
+      <c r="K37" s="33" t="n">
         <f aca="false">IFERROR(I37/J37-1,0)</f>
         <v>-0.128115359403255</v>
       </c>
-      <c r="L37" s="27" t="n">
+      <c r="L37" s="33" t="n">
         <f aca="false">ABS(D37)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0356077445432408</v>
       </c>
@@ -3533,41 +5466,41 @@
       <c r="B38" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="C38" s="13" t="n">
+      <c r="C38" s="19" t="n">
         <v>-0.00845650221457471</v>
       </c>
-      <c r="D38" s="13" t="n">
+      <c r="D38" s="19" t="n">
         <v>0.324117002670791</v>
       </c>
-      <c r="E38" s="27" t="n">
+      <c r="E38" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F38" s="27" t="n">
+      <c r="F38" s="33" t="n">
         <f aca="false">ABS(D38)*Assumptions!$E$7/10000</f>
         <v>0.000324117002670791</v>
       </c>
-      <c r="G38" s="27" t="n">
+      <c r="G38" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D38)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.30115485277192E-005</v>
       </c>
-      <c r="H38" s="27" t="n">
+      <c r="H38" s="33" t="n">
         <f aca="false">IF(E38=1,C38-F38-G38,0)</f>
         <v>-0.00880363076577322</v>
       </c>
-      <c r="I38" s="28" t="n">
+      <c r="I38" s="34" t="n">
         <f aca="false">I37*(1+H38)</f>
         <v>0.968192835963351</v>
       </c>
-      <c r="J38" s="28" t="n">
+      <c r="J38" s="34" t="n">
         <f aca="false">MAX(J37,I38)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K38" s="27" t="n">
+      <c r="K38" s="33" t="n">
         <f aca="false">IFERROR(I38/J38-1,0)</f>
         <v>-0.135791109849418</v>
       </c>
-      <c r="L38" s="27" t="n">
+      <c r="L38" s="33" t="n">
         <f aca="false">ABS(D38)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0388940403204949</v>
       </c>
@@ -3576,41 +5509,41 @@
       <c r="B39" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="C39" s="13" t="n">
+      <c r="C39" s="19" t="n">
         <v>-0.0156957410420597</v>
       </c>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="19" t="n">
         <v>0.348547989807818</v>
       </c>
-      <c r="E39" s="27" t="n">
+      <c r="E39" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F39" s="27" t="n">
+      <c r="F39" s="33" t="n">
         <f aca="false">ABS(D39)*Assumptions!$E$7/10000</f>
         <v>0.000348547989807818</v>
       </c>
-      <c r="G39" s="27" t="n">
+      <c r="G39" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D39)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.56617929939172E-005</v>
       </c>
-      <c r="H39" s="27" t="n">
+      <c r="H39" s="33" t="n">
         <f aca="false">IF(E39=1,C39-F39-G39,0)</f>
         <v>-0.0160699508248614</v>
       </c>
-      <c r="I39" s="28" t="n">
+      <c r="I39" s="34" t="n">
         <f aca="false">I38*(1+H39)</f>
         <v>0.952634024700437</v>
       </c>
-      <c r="J39" s="28" t="n">
+      <c r="J39" s="34" t="n">
         <f aca="false">MAX(J38,I39)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K39" s="27" t="n">
+      <c r="K39" s="33" t="n">
         <f aca="false">IFERROR(I39/J39-1,0)</f>
         <v>-0.149678904216546</v>
       </c>
-      <c r="L39" s="27" t="n">
+      <c r="L39" s="33" t="n">
         <f aca="false">ABS(D39)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0418257587769382</v>
       </c>
@@ -3619,41 +5552,41 @@
       <c r="B40" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="C40" s="13" t="n">
+      <c r="C40" s="19" t="n">
         <v>-0.00193509721371111</v>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="19" t="n">
         <v>0.369050179577373</v>
       </c>
-      <c r="E40" s="27" t="n">
+      <c r="E40" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F40" s="27" t="n">
+      <c r="F40" s="33" t="n">
         <f aca="false">ABS(D40)*Assumptions!$E$7/10000</f>
         <v>0.000369050179577373</v>
       </c>
-      <c r="G40" s="27" t="n">
+      <c r="G40" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D40)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.79589756126146E-005</v>
       </c>
-      <c r="H40" s="27" t="n">
+      <c r="H40" s="33" t="n">
         <f aca="false">IF(E40=1,C40-F40-G40,0)</f>
         <v>-0.0023321063689011</v>
       </c>
-      <c r="I40" s="28" t="n">
+      <c r="I40" s="34" t="n">
         <f aca="false">I39*(1+H40)</f>
         <v>0.950412380824201</v>
       </c>
-      <c r="J40" s="28" t="n">
+      <c r="J40" s="34" t="n">
         <f aca="false">MAX(J39,I40)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K40" s="27" t="n">
+      <c r="K40" s="33" t="n">
         <f aca="false">IFERROR(I40/J40-1,0)</f>
         <v>-0.151661943459633</v>
       </c>
-      <c r="L40" s="27" t="n">
+      <c r="L40" s="33" t="n">
         <f aca="false">ABS(D40)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0442860215492848</v>
       </c>
@@ -3662,41 +5595,41 @@
       <c r="B41" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="C41" s="13" t="n">
+      <c r="C41" s="19" t="n">
         <v>0.00248336663625181</v>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="19" t="n">
         <v>0.384806214371744</v>
       </c>
-      <c r="E41" s="27" t="n">
+      <c r="E41" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F41" s="27" t="n">
+      <c r="F41" s="33" t="n">
         <f aca="false">ABS(D41)*Assumptions!$E$7/10000</f>
         <v>0.000384806214371744</v>
       </c>
-      <c r="G41" s="27" t="n">
+      <c r="G41" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D41)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.97684511745614E-005</v>
       </c>
-      <c r="H41" s="27" t="n">
+      <c r="H41" s="33" t="n">
         <f aca="false">IF(E41=1,C41-F41-G41,0)</f>
         <v>0.0020687919707055</v>
       </c>
-      <c r="I41" s="28" t="n">
+      <c r="I41" s="34" t="n">
         <f aca="false">I40*(1+H41)</f>
         <v>0.952378586326509</v>
       </c>
-      <c r="J41" s="28" t="n">
+      <c r="J41" s="34" t="n">
         <f aca="false">MAX(J40,I41)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K41" s="27" t="n">
+      <c r="K41" s="33" t="n">
         <f aca="false">IFERROR(I41/J41-1,0)</f>
         <v>-0.149906908499819</v>
       </c>
-      <c r="L41" s="27" t="n">
+      <c r="L41" s="33" t="n">
         <f aca="false">ABS(D41)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0461767457246093</v>
       </c>
@@ -3705,41 +5638,41 @@
       <c r="B42" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="C42" s="13" t="n">
+      <c r="C42" s="19" t="n">
         <v>0.00714059472727621</v>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="19" t="n">
         <v>0.395187950804723</v>
       </c>
-      <c r="E42" s="27" t="n">
+      <c r="E42" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F42" s="27" t="n">
+      <c r="F42" s="33" t="n">
         <f aca="false">ABS(D42)*Assumptions!$E$7/10000</f>
         <v>0.000395187950804723</v>
       </c>
-      <c r="G42" s="27" t="n">
+      <c r="G42" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D42)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.09812306962666E-005</v>
       </c>
-      <c r="H42" s="27" t="n">
+      <c r="H42" s="33" t="n">
         <f aca="false">IF(E42=1,C42-F42-G42,0)</f>
         <v>0.00671442554577522</v>
       </c>
-      <c r="I42" s="28" t="n">
+      <c r="I42" s="34" t="n">
         <f aca="false">I41*(1+H42)</f>
         <v>0.958773261435789</v>
       </c>
-      <c r="J42" s="28" t="n">
+      <c r="J42" s="34" t="n">
         <f aca="false">MAX(J41,I42)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K42" s="27" t="n">
+      <c r="K42" s="33" t="n">
         <f aca="false">IFERROR(I42/J42-1,0)</f>
         <v>-0.144199021729963</v>
       </c>
-      <c r="L42" s="27" t="n">
+      <c r="L42" s="33" t="n">
         <f aca="false">ABS(D42)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0474225540965668</v>
       </c>
@@ -3748,41 +5681,41 @@
       <c r="B43" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="C43" s="13" t="n">
+      <c r="C43" s="19" t="n">
         <v>0.0115852980820744</v>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="19" t="n">
         <v>0.399781501806191</v>
       </c>
-      <c r="E43" s="27" t="n">
+      <c r="E43" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F43" s="27" t="n">
+      <c r="F43" s="33" t="n">
         <f aca="false">ABS(D43)*Assumptions!$E$7/10000</f>
         <v>0.000399781501806191</v>
       </c>
-      <c r="G43" s="27" t="n">
+      <c r="G43" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D43)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.15229727426071E-005</v>
       </c>
-      <c r="H43" s="27" t="n">
+      <c r="H43" s="33" t="n">
         <f aca="false">IF(E43=1,C43-F43-G43,0)</f>
         <v>0.0111539936075256</v>
       </c>
-      <c r="I43" s="28" t="n">
+      <c r="I43" s="34" t="n">
         <f aca="false">I42*(1+H43)</f>
         <v>0.96946741226491</v>
       </c>
-      <c r="J43" s="28" t="n">
+      <c r="J43" s="34" t="n">
         <f aca="false">MAX(J42,I43)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K43" s="27" t="n">
+      <c r="K43" s="33" t="n">
         <f aca="false">IFERROR(I43/J43-1,0)</f>
         <v>-0.134653423089025</v>
       </c>
-      <c r="L43" s="27" t="n">
+      <c r="L43" s="33" t="n">
         <f aca="false">ABS(D43)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0479737802167429</v>
       </c>
@@ -3791,41 +5724,41 @@
       <c r="B44" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="C44" s="13" t="n">
+      <c r="C44" s="19" t="n">
         <v>0.00538238409646321</v>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D44" s="19" t="n">
         <v>0.398403736993507</v>
       </c>
-      <c r="E44" s="27" t="n">
+      <c r="E44" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F44" s="27" t="n">
+      <c r="F44" s="33" t="n">
         <f aca="false">ABS(D44)*Assumptions!$E$7/10000</f>
         <v>0.000398403736993507</v>
       </c>
-      <c r="G44" s="27" t="n">
+      <c r="G44" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D44)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.13601570481388E-005</v>
       </c>
-      <c r="H44" s="27" t="n">
+      <c r="H44" s="33" t="n">
         <f aca="false">IF(E44=1,C44-F44-G44,0)</f>
         <v>0.00495262020242156</v>
       </c>
-      <c r="I44" s="28" t="n">
+      <c r="I44" s="34" t="n">
         <f aca="false">I43*(1+H44)</f>
         <v>0.974268816156482</v>
       </c>
-      <c r="J44" s="28" t="n">
+      <c r="J44" s="34" t="n">
         <f aca="false">MAX(J43,I44)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K44" s="27" t="n">
+      <c r="K44" s="33" t="n">
         <f aca="false">IFERROR(I44/J44-1,0)</f>
         <v>-0.130367690150119</v>
       </c>
-      <c r="L44" s="27" t="n">
+      <c r="L44" s="33" t="n">
         <f aca="false">ABS(D44)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0478084484392208</v>
       </c>
@@ -3834,41 +5767,41 @@
       <c r="B45" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="C45" s="13" t="n">
+      <c r="C45" s="19" t="n">
         <v>0.018159749795409</v>
       </c>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="19" t="n">
         <v>0.391109583501966</v>
       </c>
-      <c r="E45" s="27" t="n">
+      <c r="E45" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F45" s="27" t="n">
+      <c r="F45" s="33" t="n">
         <f aca="false">ABS(D45)*Assumptions!$E$7/10000</f>
         <v>0.000391109583501966</v>
       </c>
-      <c r="G45" s="27" t="n">
+      <c r="G45" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D45)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.05028774876638E-005</v>
       </c>
-      <c r="H45" s="27" t="n">
+      <c r="H45" s="33" t="n">
         <f aca="false">IF(E45=1,C45-F45-G45,0)</f>
         <v>0.0177381373344194</v>
       </c>
-      <c r="I45" s="28" t="n">
+      <c r="I45" s="34" t="n">
         <f aca="false">I44*(1+H45)</f>
         <v>0.991550530218108</v>
       </c>
-      <c r="J45" s="28" t="n">
+      <c r="J45" s="34" t="n">
         <f aca="false">MAX(J44,I45)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K45" s="27" t="n">
+      <c r="K45" s="33" t="n">
         <f aca="false">IFERROR(I45/J45-1,0)</f>
         <v>-0.114942032807554</v>
       </c>
-      <c r="L45" s="27" t="n">
+      <c r="L45" s="33" t="n">
         <f aca="false">ABS(D45)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0469331500202359</v>
       </c>
@@ -3877,41 +5810,41 @@
       <c r="B46" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="C46" s="13" t="n">
+      <c r="C46" s="19" t="n">
         <v>0.0196483099882406</v>
       </c>
-      <c r="D46" s="13" t="n">
+      <c r="D46" s="19" t="n">
         <v>0.378189836213242</v>
       </c>
-      <c r="E46" s="27" t="n">
+      <c r="E46" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F46" s="27" t="n">
+      <c r="F46" s="33" t="n">
         <f aca="false">ABS(D46)*Assumptions!$E$7/10000</f>
         <v>0.000378189836213242</v>
       </c>
-      <c r="G46" s="27" t="n">
+      <c r="G46" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D46)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.90040004641783E-005</v>
       </c>
-      <c r="H46" s="27" t="n">
+      <c r="H46" s="33" t="n">
         <f aca="false">IF(E46=1,C46-F46-G46,0)</f>
         <v>0.0192411161515632</v>
       </c>
-      <c r="I46" s="28" t="n">
+      <c r="I46" s="34" t="n">
         <f aca="false">I45*(1+H46)</f>
         <v>1.01062906914018</v>
       </c>
-      <c r="J46" s="28" t="n">
+      <c r="J46" s="34" t="n">
         <f aca="false">MAX(J45,I46)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K46" s="27" t="n">
+      <c r="K46" s="33" t="n">
         <f aca="false">IFERROR(I46/J46-1,0)</f>
         <v>-0.0979125296599376</v>
       </c>
-      <c r="L46" s="27" t="n">
+      <c r="L46" s="33" t="n">
         <f aca="false">ABS(D46)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.045382780345589</v>
       </c>
@@ -3920,41 +5853,41 @@
       <c r="B47" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="C47" s="13" t="n">
+      <c r="C47" s="19" t="n">
         <v>0.0197108728327755</v>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="19" t="n">
         <v>0.360159564681117</v>
       </c>
-      <c r="E47" s="27" t="n">
+      <c r="E47" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F47" s="27" t="n">
+      <c r="F47" s="33" t="n">
         <f aca="false">ABS(D47)*Assumptions!$E$7/10000</f>
         <v>0.000360159564681117</v>
       </c>
-      <c r="G47" s="27" t="n">
+      <c r="G47" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D47)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.69547651875787E-005</v>
       </c>
-      <c r="H47" s="27" t="n">
+      <c r="H47" s="33" t="n">
         <f aca="false">IF(E47=1,C47-F47-G47,0)</f>
         <v>0.0193237585029068</v>
       </c>
-      <c r="I47" s="28" t="n">
+      <c r="I47" s="34" t="n">
         <f aca="false">I46*(1+H47)</f>
         <v>1.03015822120826</v>
       </c>
-      <c r="J47" s="28" t="n">
+      <c r="J47" s="34" t="n">
         <f aca="false">MAX(J46,I47)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K47" s="27" t="n">
+      <c r="K47" s="33" t="n">
         <f aca="false">IFERROR(I47/J47-1,0)</f>
         <v>-0.080480809234588</v>
       </c>
-      <c r="L47" s="27" t="n">
+      <c r="L47" s="33" t="n">
         <f aca="false">ABS(D47)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.043219147761734</v>
       </c>
@@ -3963,41 +5896,41 @@
       <c r="B48" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="C48" s="13" t="n">
+      <c r="C48" s="19" t="n">
         <v>0.0183566992284292</v>
       </c>
-      <c r="D48" s="13" t="n">
+      <c r="D48" s="19" t="n">
         <v>0.337737578933764</v>
       </c>
-      <c r="E48" s="27" t="n">
+      <c r="E48" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F48" s="27" t="n">
+      <c r="F48" s="33" t="n">
         <f aca="false">ABS(D48)*Assumptions!$E$7/10000</f>
         <v>0.000337737578933764</v>
       </c>
-      <c r="G48" s="27" t="n">
+      <c r="G48" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D48)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.44772262696531E-005</v>
       </c>
-      <c r="H48" s="27" t="n">
+      <c r="H48" s="33" t="n">
         <f aca="false">IF(E48=1,C48-F48-G48,0)</f>
         <v>0.0179944844232258</v>
       </c>
-      <c r="I48" s="28" t="n">
+      <c r="I48" s="34" t="n">
         <f aca="false">I47*(1+H48)</f>
         <v>1.04869538727325</v>
       </c>
-      <c r="J48" s="28" t="n">
+      <c r="J48" s="34" t="n">
         <f aca="false">MAX(J47,I48)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K48" s="27" t="n">
+      <c r="K48" s="33" t="n">
         <f aca="false">IFERROR(I48/J48-1,0)</f>
         <v>-0.0639345354795027</v>
       </c>
-      <c r="L48" s="27" t="n">
+      <c r="L48" s="33" t="n">
         <f aca="false">ABS(D48)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0405285094720517</v>
       </c>
@@ -4006,41 +5939,41 @@
       <c r="B49" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="C49" s="13" t="n">
+      <c r="C49" s="19" t="n">
         <v>0.00574015432484417</v>
       </c>
-      <c r="D49" s="13" t="n">
+      <c r="D49" s="19" t="n">
         <v>0.311817772786264</v>
       </c>
-      <c r="E49" s="27" t="n">
+      <c r="E49" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F49" s="27" t="n">
+      <c r="F49" s="33" t="n">
         <f aca="false">ABS(D49)*Assumptions!$E$7/10000</f>
         <v>0.000311817772786264</v>
       </c>
-      <c r="G49" s="27" t="n">
+      <c r="G49" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D49)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.17142293979423E-005</v>
       </c>
-      <c r="H49" s="27" t="n">
+      <c r="H49" s="33" t="n">
         <f aca="false">IF(E49=1,C49-F49-G49,0)</f>
         <v>0.00540662232265996</v>
       </c>
-      <c r="I49" s="28" t="n">
+      <c r="I49" s="34" t="n">
         <f aca="false">I48*(1+H49)</f>
         <v>1.05436528716375</v>
       </c>
-      <c r="J49" s="28" t="n">
+      <c r="J49" s="34" t="n">
         <f aca="false">MAX(J48,I49)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K49" s="27" t="n">
+      <c r="K49" s="33" t="n">
         <f aca="false">IFERROR(I49/J49-1,0)</f>
         <v>-0.0588735830435551</v>
       </c>
-      <c r="L49" s="27" t="n">
+      <c r="L49" s="33" t="n">
         <f aca="false">ABS(D49)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0374181327343517</v>
       </c>
@@ -4049,41 +5982,41 @@
       <c r="B50" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="C50" s="13" t="n">
+      <c r="C50" s="19" t="n">
         <v>0.0121436062989767</v>
       </c>
-      <c r="D50" s="13" t="n">
+      <c r="D50" s="19" t="n">
         <v>0.283433487115037</v>
       </c>
-      <c r="E50" s="27" t="n">
+      <c r="E50" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F50" s="27" t="n">
+      <c r="F50" s="33" t="n">
         <f aca="false">ABS(D50)*Assumptions!$E$7/10000</f>
         <v>0.000283433487115037</v>
       </c>
-      <c r="G50" s="27" t="n">
+      <c r="G50" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D50)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>1.88178439943224E-005</v>
       </c>
-      <c r="H50" s="27" t="n">
+      <c r="H50" s="33" t="n">
         <f aca="false">IF(E50=1,C50-F50-G50,0)</f>
         <v>0.0118413549678673</v>
       </c>
-      <c r="I50" s="28" t="n">
+      <c r="I50" s="34" t="n">
         <f aca="false">I49*(1+H50)</f>
         <v>1.06685040079486</v>
       </c>
-      <c r="J50" s="28" t="n">
+      <c r="J50" s="34" t="n">
         <f aca="false">MAX(J49,I50)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K50" s="27" t="n">
+      <c r="K50" s="33" t="n">
         <f aca="false">IFERROR(I50/J50-1,0)</f>
         <v>-0.0477293710707368</v>
       </c>
-      <c r="L50" s="27" t="n">
+      <c r="L50" s="33" t="n">
         <f aca="false">ABS(D50)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0340120184538044</v>
       </c>
@@ -4092,41 +6025,41 @@
       <c r="B51" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="C51" s="13" t="n">
+      <c r="C51" s="19" t="n">
         <v>0.0079464572032407</v>
       </c>
-      <c r="D51" s="13" t="n">
+      <c r="D51" s="19" t="n">
         <v>0.253716313818004</v>
       </c>
-      <c r="E51" s="27" t="n">
+      <c r="E51" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F51" s="27" t="n">
+      <c r="F51" s="33" t="n">
         <f aca="false">ABS(D51)*Assumptions!$E$7/10000</f>
         <v>0.000253716313818004</v>
       </c>
-      <c r="G51" s="27" t="n">
+      <c r="G51" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D51)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>1.5937335432354E-005</v>
       </c>
-      <c r="H51" s="27" t="n">
+      <c r="H51" s="33" t="n">
         <f aca="false">IF(E51=1,C51-F51-G51,0)</f>
         <v>0.00767680355399034</v>
       </c>
-      <c r="I51" s="28" t="n">
+      <c r="I51" s="34" t="n">
         <f aca="false">I50*(1+H51)</f>
         <v>1.07504040174325</v>
       </c>
-      <c r="J51" s="28" t="n">
+      <c r="J51" s="34" t="n">
         <f aca="false">MAX(J50,I51)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K51" s="27" t="n">
+      <c r="K51" s="33" t="n">
         <f aca="false">IFERROR(I51/J51-1,0)</f>
         <v>-0.0404189765222121</v>
       </c>
-      <c r="L51" s="27" t="n">
+      <c r="L51" s="33" t="n">
         <f aca="false">ABS(D51)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0304459576581605</v>
       </c>
@@ -4135,41 +6068,41 @@
       <c r="B52" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="C52" s="13" t="n">
+      <c r="C52" s="19" t="n">
         <v>0.0035837128016564</v>
       </c>
-      <c r="D52" s="13" t="n">
+      <c r="D52" s="19" t="n">
         <v>0.276149017183447</v>
       </c>
-      <c r="E52" s="27" t="n">
+      <c r="E52" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F52" s="27" t="n">
+      <c r="F52" s="33" t="n">
         <f aca="false">ABS(D52)*Assumptions!$E$7/10000</f>
         <v>0.000276149017183447</v>
       </c>
-      <c r="G52" s="27" t="n">
+      <c r="G52" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D52)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>1.80970745999181E-005</v>
       </c>
-      <c r="H52" s="27" t="n">
+      <c r="H52" s="33" t="n">
         <f aca="false">IF(E52=1,C52-F52-G52,0)</f>
         <v>0.00328946670987304</v>
       </c>
-      <c r="I52" s="28" t="n">
+      <c r="I52" s="34" t="n">
         <f aca="false">I51*(1+H52)</f>
         <v>1.07857671135656</v>
       </c>
-      <c r="J52" s="28" t="n">
+      <c r="J52" s="34" t="n">
         <f aca="false">MAX(J51,I52)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K52" s="27" t="n">
+      <c r="K52" s="33" t="n">
         <f aca="false">IFERROR(I52/J52-1,0)</f>
         <v>-0.037262466690056</v>
       </c>
-      <c r="L52" s="27" t="n">
+      <c r="L52" s="33" t="n">
         <f aca="false">ABS(D52)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0331378820620136</v>
       </c>
@@ -4178,41 +6111,41 @@
       <c r="B53" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="C53" s="13" t="n">
+      <c r="C53" s="19" t="n">
         <v>-0.000501354580917067</v>
       </c>
-      <c r="D53" s="13" t="n">
+      <c r="D53" s="19" t="n">
         <v>0.304971869387789</v>
       </c>
-      <c r="E53" s="27" t="n">
+      <c r="E53" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F53" s="27" t="n">
+      <c r="F53" s="33" t="n">
         <f aca="false">ABS(D53)*Assumptions!$E$7/10000</f>
         <v>0.000304971869387789</v>
       </c>
-      <c r="G53" s="27" t="n">
+      <c r="G53" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D53)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.10030708111311E-005</v>
       </c>
-      <c r="H53" s="27" t="n">
+      <c r="H53" s="33" t="n">
         <f aca="false">IF(E53=1,C53-F53-G53,0)</f>
         <v>-0.000827329521115987</v>
       </c>
-      <c r="I53" s="28" t="n">
+      <c r="I53" s="34" t="n">
         <f aca="false">I52*(1+H53)</f>
         <v>1.07768437300246</v>
       </c>
-      <c r="J53" s="28" t="n">
+      <c r="J53" s="34" t="n">
         <f aca="false">MAX(J52,I53)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K53" s="27" t="n">
+      <c r="K53" s="33" t="n">
         <f aca="false">IFERROR(I53/J53-1,0)</f>
         <v>-0.0380589678724497</v>
       </c>
-      <c r="L53" s="27" t="n">
+      <c r="L53" s="33" t="n">
         <f aca="false">ABS(D53)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0365966243265347</v>
       </c>
@@ -4221,41 +6154,41 @@
       <c r="B54" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="C54" s="13" t="n">
+      <c r="C54" s="19" t="n">
         <v>-0.0139052502583773</v>
       </c>
-      <c r="D54" s="13" t="n">
+      <c r="D54" s="19" t="n">
         <v>0.331603166633405</v>
       </c>
-      <c r="E54" s="27" t="n">
+      <c r="E54" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F54" s="27" t="n">
+      <c r="F54" s="33" t="n">
         <f aca="false">ABS(D54)*Assumptions!$E$7/10000</f>
         <v>0.000331603166633405</v>
       </c>
-      <c r="G54" s="27" t="n">
+      <c r="G54" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D54)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.38133846781968E-005</v>
       </c>
-      <c r="H54" s="27" t="n">
+      <c r="H54" s="33" t="n">
         <f aca="false">IF(E54=1,C54-F54-G54,0)</f>
         <v>-0.0142606668096889</v>
       </c>
-      <c r="I54" s="28" t="n">
+      <c r="I54" s="34" t="n">
         <f aca="false">I53*(1+H54)</f>
         <v>1.06231587523307</v>
       </c>
-      <c r="J54" s="28" t="n">
+      <c r="J54" s="34" t="n">
         <f aca="false">MAX(J53,I54)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K54" s="27" t="n">
+      <c r="K54" s="33" t="n">
         <f aca="false">IFERROR(I54/J54-1,0)</f>
         <v>-0.051776888422189</v>
       </c>
-      <c r="L54" s="27" t="n">
+      <c r="L54" s="33" t="n">
         <f aca="false">ABS(D54)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0397923799960086</v>
       </c>
@@ -4264,41 +6197,41 @@
       <c r="B55" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="C55" s="13" t="n">
+      <c r="C55" s="19" t="n">
         <v>-0.00630773479296565</v>
       </c>
-      <c r="D55" s="13" t="n">
+      <c r="D55" s="19" t="n">
         <v>0.354981203139031</v>
       </c>
-      <c r="E55" s="27" t="n">
+      <c r="E55" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F55" s="27" t="n">
+      <c r="F55" s="33" t="n">
         <f aca="false">ABS(D55)*Assumptions!$E$7/10000</f>
         <v>0.000354981203139031</v>
       </c>
-      <c r="G55" s="27" t="n">
+      <c r="G55" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D55)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.63755278174248E-005</v>
       </c>
-      <c r="H55" s="27" t="n">
+      <c r="H55" s="33" t="n">
         <f aca="false">IF(E55=1,C55-F55-G55,0)</f>
         <v>-0.00668909152392211</v>
       </c>
-      <c r="I55" s="28" t="n">
+      <c r="I55" s="34" t="n">
         <f aca="false">I54*(1+H55)</f>
         <v>1.05520994711632</v>
       </c>
-      <c r="J55" s="28" t="n">
+      <c r="J55" s="34" t="n">
         <f aca="false">MAX(J54,I55)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K55" s="27" t="n">
+      <c r="K55" s="33" t="n">
         <f aca="false">IFERROR(I55/J55-1,0)</f>
         <v>-0.0581196396006312</v>
       </c>
-      <c r="L55" s="27" t="n">
+      <c r="L55" s="33" t="n">
         <f aca="false">ABS(D55)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0425977443766837</v>
       </c>
@@ -4307,41 +6240,41 @@
       <c r="B56" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="C56" s="13" t="n">
+      <c r="C56" s="19" t="n">
         <v>-0.00750596791669256</v>
       </c>
-      <c r="D56" s="13" t="n">
+      <c r="D56" s="19" t="n">
         <v>0.374173970362848</v>
       </c>
-      <c r="E56" s="27" t="n">
+      <c r="E56" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F56" s="27" t="n">
+      <c r="F56" s="33" t="n">
         <f aca="false">ABS(D56)*Assumptions!$E$7/10000</f>
         <v>0.000374173970362848</v>
       </c>
-      <c r="G56" s="27" t="n">
+      <c r="G56" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D56)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.85432539970961E-005</v>
       </c>
-      <c r="H56" s="27" t="n">
+      <c r="H56" s="33" t="n">
         <f aca="false">IF(E56=1,C56-F56-G56,0)</f>
         <v>-0.00790868514105251</v>
       </c>
-      <c r="I56" s="28" t="n">
+      <c r="I56" s="34" t="n">
         <f aca="false">I55*(1+H56)</f>
         <v>1.04686462388687</v>
       </c>
-      <c r="J56" s="28" t="n">
+      <c r="J56" s="34" t="n">
         <f aca="false">MAX(J55,I56)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K56" s="27" t="n">
+      <c r="K56" s="33" t="n">
         <f aca="false">IFERROR(I56/J56-1,0)</f>
         <v>-0.0655686748115708</v>
       </c>
-      <c r="L56" s="27" t="n">
+      <c r="L56" s="33" t="n">
         <f aca="false">ABS(D56)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0449008764435418</v>
       </c>
@@ -4350,41 +6283,41 @@
       <c r="B57" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="C57" s="13" t="n">
+      <c r="C57" s="19" t="n">
         <v>-0.00743558260759404</v>
       </c>
-      <c r="D57" s="13" t="n">
+      <c r="D57" s="19" t="n">
         <v>0.388416313241921</v>
       </c>
-      <c r="E57" s="27" t="n">
+      <c r="E57" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F57" s="27" t="n">
+      <c r="F57" s="33" t="n">
         <f aca="false">ABS(D57)*Assumptions!$E$7/10000</f>
         <v>0.000388416313241921</v>
       </c>
-      <c r="G57" s="27" t="n">
+      <c r="G57" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D57)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.0188345819519E-005</v>
       </c>
-      <c r="H57" s="27" t="n">
+      <c r="H57" s="33" t="n">
         <f aca="false">IF(E57=1,C57-F57-G57,0)</f>
         <v>-0.00785418726665548</v>
       </c>
-      <c r="I57" s="28" t="n">
+      <c r="I57" s="34" t="n">
         <f aca="false">I56*(1+H57)</f>
         <v>1.03864235308802</v>
       </c>
-      <c r="J57" s="28" t="n">
+      <c r="J57" s="34" t="n">
         <f aca="false">MAX(J56,I57)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K57" s="27" t="n">
+      <c r="K57" s="33" t="n">
         <f aca="false">IFERROR(I57/J57-1,0)</f>
         <v>-0.0729078734274297</v>
       </c>
-      <c r="L57" s="27" t="n">
+      <c r="L57" s="33" t="n">
         <f aca="false">ABS(D57)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0466099575890305</v>
       </c>
@@ -4393,41 +6326,41 @@
       <c r="B58" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="C58" s="13" t="n">
+      <c r="C58" s="19" t="n">
         <v>-0.00617639494320523</v>
       </c>
-      <c r="D58" s="13" t="n">
+      <c r="D58" s="19" t="n">
         <v>0.397140434509974</v>
       </c>
-      <c r="E58" s="27" t="n">
+      <c r="E58" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F58" s="27" t="n">
+      <c r="F58" s="33" t="n">
         <f aca="false">ABS(D58)*Assumptions!$E$7/10000</f>
         <v>0.000397140434509974</v>
       </c>
-      <c r="G58" s="27" t="n">
+      <c r="G58" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D58)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.12111149902454E-005</v>
       </c>
-      <c r="H58" s="27" t="n">
+      <c r="H58" s="33" t="n">
         <f aca="false">IF(E58=1,C58-F58-G58,0)</f>
         <v>-0.00660474649270545</v>
       </c>
-      <c r="I58" s="28" t="n">
+      <c r="I58" s="34" t="n">
         <f aca="false">I57*(1+H58)</f>
         <v>1.03178238364929</v>
       </c>
-      <c r="J58" s="28" t="n">
+      <c r="J58" s="34" t="n">
         <f aca="false">MAX(J57,I58)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K58" s="27" t="n">
+      <c r="K58" s="33" t="n">
         <f aca="false">IFERROR(I58/J58-1,0)</f>
         <v>-0.0790310818988247</v>
       </c>
-      <c r="L58" s="27" t="n">
+      <c r="L58" s="33" t="n">
         <f aca="false">ABS(D58)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0476568521411969</v>
       </c>
@@ -4436,41 +6369,41 @@
       <c r="B59" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="C59" s="13" t="n">
+      <c r="C59" s="19" t="n">
         <v>-0.013942149190867</v>
       </c>
-      <c r="D59" s="13" t="n">
+      <c r="D59" s="19" t="n">
         <v>0.399998530982606</v>
       </c>
-      <c r="E59" s="27" t="n">
+      <c r="E59" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F59" s="27" t="n">
+      <c r="F59" s="33" t="n">
         <f aca="false">ABS(D59)*Assumptions!$E$7/10000</f>
         <v>0.000399998530982606</v>
       </c>
-      <c r="G59" s="27" t="n">
+      <c r="G59" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D59)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.15486455158409E-005</v>
       </c>
-      <c r="H59" s="27" t="n">
+      <c r="H59" s="33" t="n">
         <f aca="false">IF(E59=1,C59-F59-G59,0)</f>
         <v>-0.0143736963673654</v>
       </c>
-      <c r="I59" s="28" t="n">
+      <c r="I59" s="34" t="n">
         <f aca="false">I58*(1+H59)</f>
         <v>1.01695185694952</v>
       </c>
-      <c r="J59" s="28" t="n">
+      <c r="J59" s="34" t="n">
         <f aca="false">MAX(J58,I59)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K59" s="27" t="n">
+      <c r="K59" s="33" t="n">
         <f aca="false">IFERROR(I59/J59-1,0)</f>
         <v>-0.0922688094913921</v>
       </c>
-      <c r="L59" s="27" t="n">
+      <c r="L59" s="33" t="n">
         <f aca="false">ABS(D59)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0479998237179127</v>
       </c>
@@ -4479,41 +6412,41 @@
       <c r="B60" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="C60" s="13" t="n">
+      <c r="C60" s="19" t="n">
         <v>-0.00105545697169086</v>
       </c>
-      <c r="D60" s="13" t="n">
+      <c r="D60" s="19" t="n">
         <v>0.396876659372698</v>
       </c>
-      <c r="E60" s="27" t="n">
+      <c r="E60" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F60" s="27" t="n">
+      <c r="F60" s="33" t="n">
         <f aca="false">ABS(D60)*Assumptions!$E$7/10000</f>
         <v>0.000396876659372698</v>
       </c>
-      <c r="G60" s="27" t="n">
+      <c r="G60" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D60)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.11800251731657E-005</v>
       </c>
-      <c r="H60" s="27" t="n">
+      <c r="H60" s="33" t="n">
         <f aca="false">IF(E60=1,C60-F60-G60,0)</f>
         <v>-0.00148351365623672</v>
       </c>
-      <c r="I60" s="28" t="n">
+      <c r="I60" s="34" t="n">
         <f aca="false">I59*(1+H60)</f>
         <v>1.015443194982</v>
       </c>
-      <c r="J60" s="28" t="n">
+      <c r="J60" s="34" t="n">
         <f aca="false">MAX(J59,I60)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K60" s="27" t="n">
+      <c r="K60" s="33" t="n">
         <f aca="false">IFERROR(I60/J60-1,0)</f>
         <v>-0.0936154411087037</v>
       </c>
-      <c r="L60" s="27" t="n">
+      <c r="L60" s="33" t="n">
         <f aca="false">ABS(D60)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0476251991247238</v>
       </c>
@@ -4522,41 +6455,41 @@
       <c r="B61" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="C61" s="13" t="n">
+      <c r="C61" s="19" t="n">
         <v>0.00208927946906418</v>
       </c>
-      <c r="D61" s="13" t="n">
+      <c r="D61" s="19" t="n">
         <v>0.387899278849701</v>
       </c>
-      <c r="E61" s="27" t="n">
+      <c r="E61" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F61" s="27" t="n">
+      <c r="F61" s="33" t="n">
         <f aca="false">ABS(D61)*Assumptions!$E$7/10000</f>
         <v>0.000387899278849701</v>
       </c>
-      <c r="G61" s="27" t="n">
+      <c r="G61" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D61)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>3.01280887559377E-005</v>
       </c>
-      <c r="H61" s="27" t="n">
+      <c r="H61" s="33" t="n">
         <f aca="false">IF(E61=1,C61-F61-G61,0)</f>
         <v>0.00167125210145854</v>
       </c>
-      <c r="I61" s="28" t="n">
+      <c r="I61" s="34" t="n">
         <f aca="false">I60*(1+H61)</f>
         <v>1.01714025655552</v>
       </c>
-      <c r="J61" s="28" t="n">
+      <c r="J61" s="34" t="n">
         <f aca="false">MAX(J60,I61)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K61" s="27" t="n">
+      <c r="K61" s="33" t="n">
         <f aca="false">IFERROR(I61/J61-1,0)</f>
         <v>-0.092100644009927</v>
       </c>
-      <c r="L61" s="27" t="n">
+      <c r="L61" s="33" t="n">
         <f aca="false">ABS(D61)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0465479134619641</v>
       </c>
@@ -4565,41 +6498,41 @@
       <c r="B62" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="C62" s="13" t="n">
+      <c r="C62" s="19" t="n">
         <v>0.00507084643567315</v>
       </c>
-      <c r="D62" s="13" t="n">
+      <c r="D62" s="19" t="n">
         <v>0.373424289245306</v>
       </c>
-      <c r="E62" s="27" t="n">
+      <c r="E62" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F62" s="27" t="n">
+      <c r="F62" s="33" t="n">
         <f aca="false">ABS(D62)*Assumptions!$E$7/10000</f>
         <v>0.000373424289245306</v>
       </c>
-      <c r="G62" s="27" t="n">
+      <c r="G62" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D62)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.84575146681851E-005</v>
       </c>
-      <c r="H62" s="27" t="n">
+      <c r="H62" s="33" t="n">
         <f aca="false">IF(E62=1,C62-F62-G62,0)</f>
         <v>0.00466896463175966</v>
       </c>
-      <c r="I62" s="28" t="n">
+      <c r="I62" s="34" t="n">
         <f aca="false">I61*(1+H62)</f>
         <v>1.02188924843892</v>
       </c>
-      <c r="J62" s="28" t="n">
+      <c r="J62" s="34" t="n">
         <f aca="false">MAX(J61,I62)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K62" s="27" t="n">
+      <c r="K62" s="33" t="n">
         <f aca="false">IFERROR(I62/J62-1,0)</f>
         <v>-0.0878616940276119</v>
       </c>
-      <c r="L62" s="27" t="n">
+      <c r="L62" s="33" t="n">
         <f aca="false">ABS(D62)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0448109147094367</v>
       </c>
@@ -4608,41 +6541,41 @@
       <c r="B63" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="C63" s="13" t="n">
+      <c r="C63" s="19" t="n">
         <v>0.00748911701523658</v>
       </c>
-      <c r="D63" s="13" t="n">
+      <c r="D63" s="19" t="n">
         <v>0.354028762716568</v>
       </c>
-      <c r="E63" s="27" t="n">
+      <c r="E63" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F63" s="27" t="n">
+      <c r="F63" s="33" t="n">
         <f aca="false">ABS(D63)*Assumptions!$E$7/10000</f>
         <v>0.000354028762716568</v>
       </c>
-      <c r="G63" s="27" t="n">
+      <c r="G63" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D63)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.6269447858918E-005</v>
       </c>
-      <c r="H63" s="27" t="n">
+      <c r="H63" s="33" t="n">
         <f aca="false">IF(E63=1,C63-F63-G63,0)</f>
         <v>0.00710881880466109</v>
       </c>
-      <c r="I63" s="28" t="n">
+      <c r="I63" s="34" t="n">
         <f aca="false">I62*(1+H63)</f>
         <v>1.02915367394451</v>
       </c>
-      <c r="J63" s="28" t="n">
+      <c r="J63" s="34" t="n">
         <f aca="false">MAX(J62,I63)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K63" s="27" t="n">
+      <c r="K63" s="33" t="n">
         <f aca="false">IFERROR(I63/J63-1,0)</f>
         <v>-0.0813774680856637</v>
       </c>
-      <c r="L63" s="27" t="n">
+      <c r="L63" s="33" t="n">
         <f aca="false">ABS(D63)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0424834515259882</v>
       </c>
@@ -4651,41 +6584,41 @@
       <c r="B64" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="C64" s="13" t="n">
+      <c r="C64" s="19" t="n">
         <v>-0.00098943569946022</v>
       </c>
-      <c r="D64" s="13" t="n">
+      <c r="D64" s="19" t="n">
         <v>0.330485937700065</v>
       </c>
-      <c r="E64" s="27" t="n">
+      <c r="E64" s="33" t="n">
         <f aca="false">IF(AND(Assumptions!$E$18&gt;=1,Assumptions!$E$19=1),1,0)</f>
         <v>1</v>
       </c>
-      <c r="F64" s="27" t="n">
+      <c r="F64" s="33" t="n">
         <f aca="false">ABS(D64)*Assumptions!$E$7/10000</f>
         <v>0.000330485937700065</v>
       </c>
-      <c r="G64" s="27" t="n">
+      <c r="G64" s="33" t="n">
         <f aca="false">Assumptions!$E$8*(ABS(D64)*Assumptions!$E$9/Assumptions!$E$10)^1.5</f>
         <v>2.36931389301999E-005</v>
       </c>
-      <c r="H64" s="27" t="n">
+      <c r="H64" s="33" t="n">
         <f aca="false">IF(E64=1,C64-F64-G64,0)</f>
         <v>-0.00134361477609049</v>
       </c>
-      <c r="I64" s="28" t="n">
+      <c r="I64" s="34" t="n">
         <f aca="false">I63*(1+H64)</f>
         <v>1.02777088786133</v>
       </c>
-      <c r="J64" s="28" t="n">
+      <c r="J64" s="34" t="n">
         <f aca="false">MAX(J63,I64)</f>
         <v>1.12032269859507</v>
       </c>
-      <c r="K64" s="27" t="n">
+      <c r="K64" s="33" t="n">
         <f aca="false">IFERROR(I64/J64-1,0)</f>
         <v>-0.0826117428931935</v>
       </c>
-      <c r="L64" s="27" t="n">
+      <c r="L64" s="33" t="n">
         <f aca="false">ABS(D64)*Assumptions!$E$9/Assumptions!$E$10</f>
         <v>0.0396583125240078</v>
       </c>
@@ -4704,7 +6637,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4720,152 +6653,152 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>68</v>
+      <c r="B4" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="27" t="n">
+        <v>168</v>
+      </c>
+      <c r="C5" s="33" t="n">
         <f aca="false">AVERAGE(Backtest!C5:C64)*Assumptions!E5</f>
         <v>0.0106418518703173</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="33" t="n">
         <f aca="false">AVERAGE(Backtest!H5:H64)*Assumptions!E5</f>
         <v>0.00614777731234425</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="27" t="n">
+        <v>170</v>
+      </c>
+      <c r="C6" s="33" t="n">
         <f aca="false">STDEVP(Backtest!C5:C64)*SQRT(Assumptions!E5)</f>
         <v>0.0366220319407769</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="33" t="n">
         <f aca="false">STDEVP(Backtest!H5:H64)*SQRT(Assumptions!E5)</f>
         <v>0.0365679857703514</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="29" t="n">
+        <v>172</v>
+      </c>
+      <c r="C7" s="35" t="n">
         <f aca="false">IFERROR((AVERAGE(Backtest!C5:C64)-Assumptions!E6)/STDEVP(Backtest!C5:C64)*SQRT(Assumptions!E5),0)</f>
         <v>-0.364757153597724</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="35" t="n">
         <f aca="false">IFERROR((AVERAGE(Backtest!H5:H64)-Assumptions!E6)/STDEVP(Backtest!H5:H64)*SQRT(Assumptions!E5),0)</f>
         <v>-0.48819267213044</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>74</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="29" t="n">
+        <v>174</v>
+      </c>
+      <c r="C8" s="35" t="n">
         <f aca="false">IFERROR((AVERAGE(Backtest!C5:C64)-Assumptions!E6)/SQRT(SUMPRODUCT((Backtest!C5:C64&lt;Assumptions!E6)*(Backtest!C5:C64-Assumptions!E6)^2)/COUNT(Backtest!C5:C64))*SQRT(Assumptions!E5),0)</f>
         <v>-0.476754711518125</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="35" t="n">
         <f aca="false">IFERROR((AVERAGE(Backtest!H5:H64)-Assumptions!E6)/SQRT(SUMPRODUCT((Backtest!H5:H64&lt;Assumptions!E6)*(Backtest!H5:H64-Assumptions!E6)^2)/COUNT(Backtest!H5:H64))*SQRT(Assumptions!E5),0)</f>
         <v>-0.620154480028033</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>76</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="27" t="n">
+        <v>176</v>
+      </c>
+      <c r="C9" s="33" t="n">
         <f aca="false">MIN(Backtest!K5:K64)</f>
         <v>-0.151661943459633</v>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="33" t="n">
         <f aca="false">MIN(Backtest!K5:K64)</f>
         <v>-0.151661943459633</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>78</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="27" t="n">
+        <v>178</v>
+      </c>
+      <c r="C10" s="33" t="n">
         <f aca="false">COUNTIF(Backtest!C5:C64,"&gt;0")/COUNT(Backtest!C5:C64)</f>
         <v>0.5</v>
       </c>
-      <c r="D10" s="27" t="n">
+      <c r="D10" s="33" t="n">
         <f aca="false">COUNTIF(Backtest!H5:H64,"&gt;0")/COUNT(Backtest!H5:H64)</f>
         <v>0.5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>80</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="30" t="n">
+        <v>180</v>
+      </c>
+      <c r="C11" s="36" t="n">
         <f aca="false">PRODUCT(1+Backtest!C5:C64)</f>
         <v>1.01391884441607</v>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="36" t="n">
         <f aca="false">Backtest!I64</f>
         <v>1.02777088786133</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>82</v>
+        <v>181</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="27" t="n">
+        <v>182</v>
+      </c>
+      <c r="C12" s="33" t="n">
         <f aca="false">C5-D5</f>
         <v>0.00449407455797305</v>
       </c>
-      <c r="D12" s="27" t="n">
+      <c r="D12" s="33" t="n">
         <f aca="false">C5-D5</f>
         <v>0.00449407455797305</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>84</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -4882,7 +6815,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4898,7 +6831,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>85</v>
+        <v>184</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -4910,32 +6843,32 @@
       <c r="J2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>94</v>
+      <c r="B4" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4954,19 +6887,19 @@
       <c r="F5" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="G5" s="29" t="n">
+      <c r="G5" s="35" t="n">
         <f aca="false">IFERROR(AVERAGE(INDEX(Backtest!$H$5:$H$64,C5):INDEX(Backtest!$H$5:$H$64,D5))/STDEVP(INDEX(Backtest!$H$5:$H$64,C5):INDEX(Backtest!$H$5:$H$64,D5))*SQRT(Assumptions!$E$5),0)</f>
         <v>0.35364868668223</v>
       </c>
-      <c r="H5" s="29" t="n">
+      <c r="H5" s="35" t="n">
         <f aca="false">IFERROR(AVERAGE(INDEX(Backtest!$H$5:$H$64,E5):INDEX(Backtest!$H$5:$H$64,F5))/STDEVP(INDEX(Backtest!$H$5:$H$64,E5):INDEX(Backtest!$H$5:$H$64,F5))*SQRT(Assumptions!$E$5),0)</f>
         <v>-1.59257638738543</v>
       </c>
-      <c r="I5" s="27" t="n">
+      <c r="I5" s="33" t="n">
         <f aca="false">(1+INDEX(Backtest!$H$5:$H$64,E5+0))*(1+INDEX(Backtest!$H$5:$H$64,E5+1))*(1+INDEX(Backtest!$H$5:$H$64,E5+2))*(1+INDEX(Backtest!$H$5:$H$64,E5+3))*(1+INDEX(Backtest!$H$5:$H$64,E5+4))*(1+INDEX(Backtest!$H$5:$H$64,E5+5))-1</f>
         <v>-0.0193739530173593</v>
       </c>
-      <c r="J5" s="29" t="n">
+      <c r="J5" s="35" t="n">
         <f aca="false">H5-G5</f>
         <v>-1.94622507406766</v>
       </c>
@@ -4987,19 +6920,19 @@
       <c r="F6" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="G6" s="29" t="n">
+      <c r="G6" s="35" t="n">
         <f aca="false">IFERROR(AVERAGE(INDEX(Backtest!$H$5:$H$64,C6):INDEX(Backtest!$H$5:$H$64,D6))/STDEVP(INDEX(Backtest!$H$5:$H$64,C6):INDEX(Backtest!$H$5:$H$64,D6))*SQRT(Assumptions!$E$5),0)</f>
         <v>-1.24186717534081</v>
       </c>
-      <c r="H6" s="29" t="n">
+      <c r="H6" s="35" t="n">
         <f aca="false">IFERROR(AVERAGE(INDEX(Backtest!$H$5:$H$64,E6):INDEX(Backtest!$H$5:$H$64,F6))/STDEVP(INDEX(Backtest!$H$5:$H$64,E6):INDEX(Backtest!$H$5:$H$64,F6))*SQRT(Assumptions!$E$5),0)</f>
         <v>-8.26087698652777</v>
       </c>
-      <c r="I6" s="27" t="n">
+      <c r="I6" s="33" t="n">
         <f aca="false">(1+INDEX(Backtest!$H$5:$H$64,E6+0))*(1+INDEX(Backtest!$H$5:$H$64,E6+1))*(1+INDEX(Backtest!$H$5:$H$64,E6+2))*(1+INDEX(Backtest!$H$5:$H$64,E6+3))*(1+INDEX(Backtest!$H$5:$H$64,E6+4))*(1+INDEX(Backtest!$H$5:$H$64,E6+5))-1</f>
         <v>-0.0561084544238982</v>
       </c>
-      <c r="J6" s="29" t="n">
+      <c r="J6" s="35" t="n">
         <f aca="false">H6-G6</f>
         <v>-7.01900981118696</v>
       </c>
@@ -5020,19 +6953,19 @@
       <c r="F7" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="G7" s="29" t="n">
+      <c r="G7" s="35" t="n">
         <f aca="false">IFERROR(AVERAGE(INDEX(Backtest!$H$5:$H$64,C7):INDEX(Backtest!$H$5:$H$64,D7))/STDEVP(INDEX(Backtest!$H$5:$H$64,C7):INDEX(Backtest!$H$5:$H$64,D7))*SQRT(Assumptions!$E$5),0)</f>
         <v>-2.52331389838928</v>
       </c>
-      <c r="H7" s="29" t="n">
+      <c r="H7" s="35" t="n">
         <f aca="false">IFERROR(AVERAGE(INDEX(Backtest!$H$5:$H$64,E7):INDEX(Backtest!$H$5:$H$64,F7))/STDEVP(INDEX(Backtest!$H$5:$H$64,E7):INDEX(Backtest!$H$5:$H$64,F7))*SQRT(Assumptions!$E$5),0)</f>
         <v>5.58762278354152</v>
       </c>
-      <c r="I7" s="27" t="n">
+      <c r="I7" s="33" t="n">
         <f aca="false">(1+INDEX(Backtest!$H$5:$H$64,E7+0))*(1+INDEX(Backtest!$H$5:$H$64,E7+1))*(1+INDEX(Backtest!$H$5:$H$64,E7+2))*(1+INDEX(Backtest!$H$5:$H$64,E7+3))*(1+INDEX(Backtest!$H$5:$H$64,E7+4))*(1+INDEX(Backtest!$H$5:$H$64,E7+5))-1</f>
         <v>0.063358484728238</v>
       </c>
-      <c r="J7" s="29" t="n">
+      <c r="J7" s="35" t="n">
         <f aca="false">H7-G7</f>
         <v>8.1109366819308</v>
       </c>
@@ -5053,19 +6986,19 @@
       <c r="F8" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="G8" s="29" t="n">
+      <c r="G8" s="35" t="n">
         <f aca="false">IFERROR(AVERAGE(INDEX(Backtest!$H$5:$H$64,C8):INDEX(Backtest!$H$5:$H$64,D8))/STDEVP(INDEX(Backtest!$H$5:$H$64,C8):INDEX(Backtest!$H$5:$H$64,D8))*SQRT(Assumptions!$E$5),0)</f>
         <v>-0.0485836560036503</v>
       </c>
-      <c r="H8" s="29" t="n">
+      <c r="H8" s="35" t="n">
         <f aca="false">IFERROR(AVERAGE(INDEX(Backtest!$H$5:$H$64,E8):INDEX(Backtest!$H$5:$H$64,F8))/STDEVP(INDEX(Backtest!$H$5:$H$64,E8):INDEX(Backtest!$H$5:$H$64,F8))*SQRT(Assumptions!$E$5),0)</f>
         <v>6.23891157036483</v>
       </c>
-      <c r="I8" s="27" t="n">
+      <c r="I8" s="33" t="n">
         <f aca="false">(1+INDEX(Backtest!$H$5:$H$64,E8+0))*(1+INDEX(Backtest!$H$5:$H$64,E8+1))*(1+INDEX(Backtest!$H$5:$H$64,E8+2))*(1+INDEX(Backtest!$H$5:$H$64,E8+3))*(1+INDEX(Backtest!$H$5:$H$64,E8+4))*(1+INDEX(Backtest!$H$5:$H$64,E8+5))-1</f>
         <v>0.0672330178214515</v>
       </c>
-      <c r="J8" s="29" t="n">
+      <c r="J8" s="35" t="n">
         <f aca="false">H8-G8</f>
         <v>6.28749522636848</v>
       </c>
@@ -5086,19 +7019,19 @@
       <c r="F9" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="G9" s="29" t="n">
+      <c r="G9" s="35" t="n">
         <f aca="false">IFERROR(AVERAGE(INDEX(Backtest!$H$5:$H$64,C9):INDEX(Backtest!$H$5:$H$64,D9))/STDEVP(INDEX(Backtest!$H$5:$H$64,C9):INDEX(Backtest!$H$5:$H$64,D9))*SQRT(Assumptions!$E$5),0)</f>
         <v>0.686317248202471</v>
       </c>
-      <c r="H9" s="29" t="n">
+      <c r="H9" s="35" t="n">
         <f aca="false">IFERROR(AVERAGE(INDEX(Backtest!$H$5:$H$64,E9):INDEX(Backtest!$H$5:$H$64,F9))/STDEVP(INDEX(Backtest!$H$5:$H$64,E9):INDEX(Backtest!$H$5:$H$64,F9))*SQRT(Assumptions!$E$5),0)</f>
         <v>-6.51371333788564</v>
       </c>
-      <c r="I9" s="27" t="n">
+      <c r="I9" s="33" t="n">
         <f aca="false">(1+INDEX(Backtest!$H$5:$H$64,E9+0))*(1+INDEX(Backtest!$H$5:$H$64,E9+1))*(1+INDEX(Backtest!$H$5:$H$64,E9+2))*(1+INDEX(Backtest!$H$5:$H$64,E9+3))*(1+INDEX(Backtest!$H$5:$H$64,E9+4))*(1+INDEX(Backtest!$H$5:$H$64,E9+5))-1</f>
         <v>-0.0433852568987997</v>
       </c>
-      <c r="J9" s="29" t="n">
+      <c r="J9" s="35" t="n">
         <f aca="false">H9-G9</f>
         <v>-7.20003058608811</v>
       </c>
@@ -5119,19 +7052,19 @@
       <c r="F10" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="G10" s="29" t="n">
+      <c r="G10" s="35" t="n">
         <f aca="false">IFERROR(AVERAGE(INDEX(Backtest!$H$5:$H$64,C10):INDEX(Backtest!$H$5:$H$64,D10))/STDEVP(INDEX(Backtest!$H$5:$H$64,C10):INDEX(Backtest!$H$5:$H$64,D10))*SQRT(Assumptions!$E$5),0)</f>
         <v>0.34196974922452</v>
       </c>
-      <c r="H10" s="29" t="n">
+      <c r="H10" s="35" t="n">
         <f aca="false">IFERROR(AVERAGE(INDEX(Backtest!$H$5:$H$64,E10):INDEX(Backtest!$H$5:$H$64,F10))/STDEVP(INDEX(Backtest!$H$5:$H$64,E10):INDEX(Backtest!$H$5:$H$64,F10))*SQRT(Assumptions!$E$5),0)</f>
         <v>-0.315181333936739</v>
       </c>
-      <c r="I10" s="27" t="n">
+      <c r="I10" s="33" t="n">
         <f aca="false">(1+INDEX(Backtest!$H$5:$H$64,E10+0))*(1+INDEX(Backtest!$H$5:$H$64,E10+1))*(1+INDEX(Backtest!$H$5:$H$64,E10+2))*(1+INDEX(Backtest!$H$5:$H$64,E10+3))*(1+INDEX(Backtest!$H$5:$H$64,E10+4))*(1+INDEX(Backtest!$H$5:$H$64,E10+5))-1</f>
         <v>-0.00388792816347283</v>
       </c>
-      <c r="J10" s="29" t="n">
+      <c r="J10" s="35" t="n">
         <f aca="false">H10-G10</f>
         <v>-0.657151083161259</v>
       </c>
@@ -5150,7 +7083,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -5165,7 +7098,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>95</v>
+        <v>194</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -5174,171 +7107,171 @@
       <c r="G2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="31" t="n">
+      <c r="B4" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="37" t="n">
         <v>0.1</v>
       </c>
-      <c r="D4" s="31" t="n">
+      <c r="D4" s="37" t="n">
         <v>0.25</v>
       </c>
-      <c r="E4" s="31" t="n">
+      <c r="E4" s="37" t="n">
         <v>0.5</v>
       </c>
-      <c r="F4" s="31" t="n">
+      <c r="F4" s="37" t="n">
         <v>0.75</v>
       </c>
-      <c r="G4" s="31" t="n">
+      <c r="G4" s="37" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="32" t="n">
+      <c r="B5" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="33" t="n">
         <f aca="false">C$4*Assumptions!$E$7/10000+Assumptions!$E$8*(C$4*$B5/Assumptions!$E$10)^1.5</f>
         <v>0.0001002683281573</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="33" t="n">
         <f aca="false">D$4*Assumptions!$E$7/10000+Assumptions!$E$8*(D$4*$B5/Assumptions!$E$10)^1.5</f>
         <v>0.00025106066017178</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="33" t="n">
         <f aca="false">E$4*Assumptions!$E$7/10000+Assumptions!$E$8*(E$4*$B5/Assumptions!$E$10)^1.5</f>
         <v>0.000503</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="33" t="n">
         <f aca="false">F$4*Assumptions!$E$7/10000+Assumptions!$E$8*(F$4*$B5/Assumptions!$E$10)^1.5</f>
         <v>0.000755511351921262</v>
       </c>
-      <c r="G5" s="27" t="n">
+      <c r="G5" s="33" t="n">
         <f aca="false">G$4*Assumptions!$E$7/10000+Assumptions!$E$8*(G$4*$B5/Assumptions!$E$10)^1.5</f>
         <v>0.00100848528137424</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="32" t="n">
+      <c r="B6" s="38" t="n">
         <v>25</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="33" t="n">
         <f aca="false">C$4*Assumptions!$E$7/10000+Assumptions!$E$8*(C$4*$B6/Assumptions!$E$10)^1.5</f>
         <v>0.00010106066017178</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="33" t="n">
         <f aca="false">D$4*Assumptions!$E$7/10000+Assumptions!$E$8*(D$4*$B6/Assumptions!$E$10)^1.5</f>
         <v>0.000254192627457812</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="33" t="n">
         <f aca="false">E$4*Assumptions!$E$7/10000+Assumptions!$E$8*(E$4*$B6/Assumptions!$E$10)^1.5</f>
         <v>0.000511858541225631</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="33" t="n">
         <f aca="false">F$4*Assumptions!$E$7/10000+Assumptions!$E$8*(F$4*$B6/Assumptions!$E$10)^1.5</f>
         <v>0.000771785531322417</v>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="33" t="n">
         <f aca="false">G$4*Assumptions!$E$7/10000+Assumptions!$E$8*(G$4*$B6/Assumptions!$E$10)^1.5</f>
         <v>0.0010335410196625</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="32" t="n">
+      <c r="B7" s="38" t="n">
         <v>50</v>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="33" t="n">
         <f aca="false">C$4*Assumptions!$E$7/10000+Assumptions!$E$8*(C$4*$B7/Assumptions!$E$10)^1.5</f>
         <v>0.000103</v>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="33" t="n">
         <f aca="false">D$4*Assumptions!$E$7/10000+Assumptions!$E$8*(D$4*$B7/Assumptions!$E$10)^1.5</f>
         <v>0.000261858541225631</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="33" t="n">
         <f aca="false">E$4*Assumptions!$E$7/10000+Assumptions!$E$8*(E$4*$B7/Assumptions!$E$10)^1.5</f>
         <v>0.000533541019662497</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="33" t="n">
         <f aca="false">F$4*Assumptions!$E$7/10000+Assumptions!$E$8*(F$4*$B7/Assumptions!$E$10)^1.5</f>
         <v>0.000811618787719331</v>
       </c>
-      <c r="G7" s="27" t="n">
+      <c r="G7" s="33" t="n">
         <f aca="false">G$4*Assumptions!$E$7/10000+Assumptions!$E$8*(G$4*$B7/Assumptions!$E$10)^1.5</f>
         <v>0.00109486832980505</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="32" t="n">
+      <c r="B8" s="38" t="n">
         <v>100</v>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="33" t="n">
         <f aca="false">C$4*Assumptions!$E$7/10000+Assumptions!$E$8*(C$4*$B8/Assumptions!$E$10)^1.5</f>
         <v>0.000108485281374239</v>
       </c>
-      <c r="D8" s="27" t="n">
+      <c r="D8" s="33" t="n">
         <f aca="false">D$4*Assumptions!$E$7/10000+Assumptions!$E$8*(D$4*$B8/Assumptions!$E$10)^1.5</f>
         <v>0.000283541019662497</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="33" t="n">
         <f aca="false">E$4*Assumptions!$E$7/10000+Assumptions!$E$8*(E$4*$B8/Assumptions!$E$10)^1.5</f>
         <v>0.000594868329805052</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="33" t="n">
         <f aca="false">F$4*Assumptions!$E$7/10000+Assumptions!$E$8*(F$4*$B8/Assumptions!$E$10)^1.5</f>
         <v>0.000924284250579334</v>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="33" t="n">
         <f aca="false">G$4*Assumptions!$E$7/10000+Assumptions!$E$8*(G$4*$B8/Assumptions!$E$10)^1.5</f>
         <v>0.00126832815729998</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="32" t="n">
+      <c r="B9" s="38" t="n">
         <v>250</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="33" t="n">
         <f aca="false">C$4*Assumptions!$E$7/10000+Assumptions!$E$8*(C$4*$B9/Assumptions!$E$10)^1.5</f>
         <v>0.000133541019662497</v>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="33" t="n">
         <f aca="false">D$4*Assumptions!$E$7/10000+Assumptions!$E$8*(D$4*$B9/Assumptions!$E$10)^1.5</f>
         <v>0.000382582521472478</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="33" t="n">
         <f aca="false">E$4*Assumptions!$E$7/10000+Assumptions!$E$8*(E$4*$B9/Assumptions!$E$10)^1.5</f>
         <v>0.000875</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="33" t="n">
         <f aca="false">F$4*Assumptions!$E$7/10000+Assumptions!$E$8*(F$4*$B9/Assumptions!$E$10)^1.5</f>
         <v>0.00143891899015777</v>
       </c>
-      <c r="G9" s="27" t="n">
+      <c r="G9" s="33" t="n">
         <f aca="false">G$4*Assumptions!$E$7/10000+Assumptions!$E$8*(G$4*$B9/Assumptions!$E$10)^1.5</f>
         <v>0.00206066017177982</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="27" t="n">
+        <v>196</v>
+      </c>
+      <c r="C12" s="33" t="n">
         <f aca="false">MAX(Backtest!L5:L64)</f>
         <v>0.0479998237179127</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" s="27" t="n">
+        <v>197</v>
+      </c>
+      <c r="C13" s="33" t="n">
         <f aca="false">Assumptions!E11</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>99</v>
+        <v>198</v>
       </c>
       <c r="C14" s="1" t="str">
         <f aca="false">IF(C12&lt;=C13,"PASS","BREACH")</f>
@@ -5383,509 +7316,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:E13"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="40"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="27" t="n">
-        <f aca="false">-PERCENTILE(Backtest!H5:H64,1-Assumptions!E15)</f>
-        <v>0.0144585090902402</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="27" t="n">
-        <f aca="false">IFERROR(-AVERAGEIF(Backtest!H5:H64,"&lt;="&amp;-C5,Backtest!H5:H64),0)</f>
-        <v>0.018812308289703</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="27" t="n">
-        <f aca="false">-(AVERAGE(Backtest!H5:H64)+NORMSINV(1-Assumptions!E15)*STDEVP(Backtest!H5:H64))</f>
-        <v>0.0168512012830348</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="27" t="n">
-        <f aca="false">Performance!D9</f>
-        <v>-0.151661943459633</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" s="27" t="n">
-        <f aca="false">ABS(Assumptions!E17)</f>
-        <v>0.2</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" s="1" t="str">
-        <f aca="false">IF(C8&lt;=C9,"PASS","BREACH")</f>
-        <v>PASS</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C11" s="27" t="n">
-        <f aca="false">Performance!D6</f>
-        <v>0.0365679857703514</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="27" t="n">
-        <f aca="false">Assumptions!E16</f>
-        <v>0.12</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="29" t="n">
-        <f aca="false">IFERROR(C12/C11,0)</f>
-        <v>3.2815589229772</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:E2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C10">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>C10="PASS"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>C10="FAIL"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>C10="REVIEW"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>C10="BREACH"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:G9"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="16"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="D5" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E5" s="33" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F5" s="27" t="n">
-        <f aca="false">AVERAGE(Backtest!D5:D64)*D5*Assumptions!$E$7/10000+Assumptions!$E$8*(AVERAGE(Backtest!D5:D64)*D5*Assumptions!$E$9/(Assumptions!$E$10*E5))^1.5</f>
-        <v>0.000624497631362428</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <f aca="false">C5-F5</f>
-        <v>-0.120624497631362</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="D6" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <f aca="false">AVERAGE(Backtest!D5:D64)*D6*Assumptions!$E$7/10000+Assumptions!$E$8*(AVERAGE(Backtest!D5:D64)*D6*Assumptions!$E$9/(Assumptions!$E$10*E6))^1.5</f>
-        <v>0.000902745455956885</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <f aca="false">C6-F6</f>
-        <v>-0.0609027454559569</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="D7" s="33" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="33" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <f aca="false">AVERAGE(Backtest!D5:D64)*D7*Assumptions!$E$7/10000+Assumptions!$E$8*(AVERAGE(Backtest!D5:D64)*D7*Assumptions!$E$9/(Assumptions!$E$10*E7))^1.5</f>
-        <v>0.00185794073027529</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <f aca="false">C7-F7</f>
-        <v>-0.101857940730275</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="D8" s="33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E8" s="33" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <f aca="false">AVERAGE(Backtest!D5:D64)*D8*Assumptions!$E$7/10000+Assumptions!$E$8*(AVERAGE(Backtest!D5:D64)*D8*Assumptions!$E$9/(Assumptions!$E$10*E8))^1.5</f>
-        <v>0.00133493401017127</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <f aca="false">C8-F8</f>
-        <v>-0.0413349340101713</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="D9" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <f aca="false">AVERAGE(Backtest!D5:D64)*D9*Assumptions!$E$7/10000+Assumptions!$E$8*(AVERAGE(Backtest!D5:D64)*D9*Assumptions!$E$9/(Assumptions!$E$10*E9))^1.5</f>
-        <v>0.000374346542046622</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <f aca="false">C9-F9</f>
-        <v>-0.0303743465420466</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:G2"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:C13"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5" s="1" t="str">
-        <f aca="false">IF(Assumptions!E18&gt;=1,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="1" t="str">
-        <f aca="false">IF(Assumptions!E19=1,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7" s="1" t="str">
-        <f aca="false">IF(AND(Assumptions!E7&gt;0,Assumptions!E8&gt;0),"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" s="1" t="str">
-        <f aca="false">IF('Costs &amp; Capacity'!C14="PASS","PASS","BREACH")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C9" s="1" t="str">
-        <f aca="false">IF(Performance!C5&gt;=Performance!D5,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C10" s="1" t="str">
-        <f aca="false">IF(COUNT('Walk Forward'!H5:H10)=6,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C11" s="1" t="str">
-        <f aca="false">IF(Risk!C10="PASS","PASS","REVIEW")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C12" s="1" t="str">
-        <f aca="false">IF(COUNT(Backtest!H5:H64)=60,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C13" s="1" t="str">
-        <f aca="false">IF(COUNTIF(C5:C12,"FAIL")=0,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:C2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C5:C13">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>C5="PASS"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>C5="FAIL"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>C5="REVIEW"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>C5="BREACH"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>